--- a/public/exports-from-60/62761113.xlsx
+++ b/public/exports-from-60/62761113.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t xml:space="preserve">200057567</t>
+          <t xml:space="preserve">200057570</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t xml:space="preserve">200057568</t>
+          <t xml:space="preserve">200057570</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Henrik Larsen Rådgivende Ingeniørfirma A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -16864,7 +16864,7 @@
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t xml:space="preserve">311594594</t>
+          <t xml:space="preserve">311594599</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">

--- a/public/exports-from-60/62761113.xlsx
+++ b/public/exports-from-60/62761113.xlsx
@@ -4991,7 +4991,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rylevænget 7B</t>
+          <t xml:space="preserve">Rylevænget 7D</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">711974, 1300454</t>
+          <t xml:space="preserve">711975, 8777506</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -5066,26 +5066,26 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rylevænget 7D</t>
+          <t xml:space="preserve">Skolesvinget 10</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2880</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">711975, 8777506</t>
+          <t xml:space="preserve">8777389</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J68">
-        <v>113</v>
+        <v>142</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -5156,11 +5156,11 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J69">
-        <v>142</v>
+        <v>186</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolesvinget 10</t>
+          <t xml:space="preserve">Skolesvinget 4</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5226,16 +5226,16 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777389</t>
+          <t xml:space="preserve">7151447</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">40</t>
         </is>
       </c>
       <c r="J70">
-        <v>186</v>
+        <v>1085</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolesvinget 4</t>
+          <t xml:space="preserve">Skolesvinget 7</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5301,16 +5301,16 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">7151447</t>
+          <t xml:space="preserve">8777389</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">40</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J71">
-        <v>1085</v>
+        <v>132</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -5366,26 +5366,26 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolesvinget 7</t>
+          <t xml:space="preserve">Slotsparken 30</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2880</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777389</t>
+          <t xml:space="preserve">2087930</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J72">
-        <v>132</v>
+        <v>168</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slotsparken 30</t>
+          <t xml:space="preserve">Taxvej 13</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5451,16 +5451,16 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2087930</t>
+          <t xml:space="preserve">2085256</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J73">
-        <v>168</v>
+        <v>140</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taxvej 13</t>
+          <t xml:space="preserve">Taxvej 25</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -5526,16 +5526,16 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2085256</t>
+          <t xml:space="preserve">2085364</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J74">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -5606,11 +5606,11 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J75">
-        <v>120</v>
+        <v>181</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taxvej 25</t>
+          <t xml:space="preserve">Til Jernbanen 20A</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5676,16 +5676,16 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2085364</t>
+          <t xml:space="preserve">8777678</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J76">
-        <v>181</v>
+        <v>231</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -5741,17 +5741,17 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Til Jernbanen 20A</t>
+          <t xml:space="preserve">Tobaksvejen 6</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2880</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777678</t>
+          <t xml:space="preserve">100321492</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5760,7 +5760,7 @@
         </is>
       </c>
       <c r="J77">
-        <v>231</v>
+        <v>1436</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -5816,7 +5816,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tobaksvejen 6</t>
+          <t xml:space="preserve">Transformervej 15</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">100321492</t>
+          <t xml:space="preserve">711981, 2099445</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="J78">
-        <v>1436</v>
+        <v>1020</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transformervej 15</t>
+          <t xml:space="preserve">Turbinevej 10</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5901,16 +5901,16 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">711981, 2099445</t>
+          <t xml:space="preserve">2099386</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="J79">
-        <v>1020</v>
+        <v>348</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -5966,26 +5966,26 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Turbinevej 10</t>
+          <t xml:space="preserve">Valdemar Poulsens Vej 6</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2099386</t>
+          <t xml:space="preserve">711990, 2087329</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J80">
-        <v>348</v>
+        <v>2537</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -6056,11 +6056,11 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J81">
-        <v>2537</v>
+        <v>104</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -6131,11 +6131,11 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J82">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -6191,26 +6191,26 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valdemar Poulsens Vej 6</t>
+          <t xml:space="preserve">Værebrovej 82C</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2880</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">711990, 2087329</t>
+          <t xml:space="preserve">100891027</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J83">
-        <v>78</v>
+        <v>387</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
@@ -6266,26 +6266,26 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Værebrovej 82C</t>
+          <t xml:space="preserve">Wergelands Alle 2</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2880</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">100891027</t>
+          <t xml:space="preserve">2009784</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J84">
-        <v>387</v>
+        <v>143</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wergelands Alle 2</t>
+          <t xml:space="preserve">Pilegårdsvej 76</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -6351,20 +6351,20 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2009784</t>
+          <t xml:space="preserve">2098138</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J85">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">100119443</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-05-05</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pilegårdsvej 76</t>
+          <t xml:space="preserve">Pilegårdsvej 78</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2098138</t>
+          <t xml:space="preserve">2098137</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t xml:space="preserve">100119443</t>
+          <t xml:space="preserve">100123246</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -6449,7 +6449,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-05-05</t>
+          <t xml:space="preserve">2019-06-09</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6491,17 +6491,17 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pilegårdsvej 78</t>
+          <t xml:space="preserve">Taxvej 21</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2880</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2098137</t>
+          <t xml:space="preserve">2085254</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -6510,21 +6510,21 @@
         </is>
       </c>
       <c r="J87">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t xml:space="preserve">100123246</t>
+          <t xml:space="preserve">100124099</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Danakon a/s</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-09</t>
+          <t xml:space="preserve">2019-06-16</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taxvej 21</t>
+          <t xml:space="preserve">Møllemarken 27</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2085254</t>
+          <t xml:space="preserve">2017118</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -6585,21 +6585,21 @@
         </is>
       </c>
       <c r="J88">
-        <v>100</v>
+        <v>1200</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t xml:space="preserve">100124099</t>
+          <t xml:space="preserve">200021869</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Danakon a/s</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-16</t>
+          <t xml:space="preserve">2019-10-06</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllemarken 27</t>
+          <t xml:space="preserve">Taxvej 15</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2017118</t>
+          <t xml:space="preserve">2085260</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -6660,21 +6660,21 @@
         </is>
       </c>
       <c r="J89">
-        <v>1200</v>
+        <v>185</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t xml:space="preserve">200021869</t>
+          <t xml:space="preserve">200023826</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Kuben Management A/S</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-10-06</t>
+          <t xml:space="preserve">2019-11-12</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taxvej 15</t>
+          <t xml:space="preserve">Taxvej 25</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2085260</t>
+          <t xml:space="preserve">2085364</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -6735,11 +6735,11 @@
         </is>
       </c>
       <c r="J90">
-        <v>185</v>
+        <v>2047</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t xml:space="preserve">200023826</t>
+          <t xml:space="preserve">200024430</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6749,7 +6749,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-11-12</t>
+          <t xml:space="preserve">2019-11-24</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6791,30 +6791,30 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taxvej 25</t>
+          <t xml:space="preserve">Buddingevej 222</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2880</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2085364</t>
+          <t xml:space="preserve">8705979</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J91">
-        <v>2047</v>
+        <v>254</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024430</t>
+          <t xml:space="preserve">200024688</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6824,7 +6824,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-11-24</t>
+          <t xml:space="preserve">2019-11-27</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buddingevej 222</t>
+          <t xml:space="preserve">Buddingevej 224</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -6881,11 +6881,11 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J92">
-        <v>254</v>
+        <v>157</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buddingevej 224</t>
+          <t xml:space="preserve">Ilbjerg Alle 23</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -6951,30 +6951,30 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">8705979</t>
+          <t xml:space="preserve">8777687</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J93">
-        <v>157</v>
+        <v>10924</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024688</t>
+          <t xml:space="preserve">200043875</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kuben Management A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-11-27</t>
+          <t xml:space="preserve">2021-01-04</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ilbjerg Alle 23</t>
+          <t xml:space="preserve">Ilbjerg Alle 25</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -7031,15 +7031,15 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J94">
-        <v>10924</v>
+        <v>100</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043875</t>
+          <t xml:space="preserve">200043874</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ilbjerg Alle 25</t>
+          <t xml:space="preserve">Gyngemose Parkvej 28A</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -7101,20 +7101,20 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777687</t>
+          <t xml:space="preserve">2098038</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J95">
-        <v>100</v>
+        <v>3669</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043874</t>
+          <t xml:space="preserve">200054667</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-01-04</t>
+          <t xml:space="preserve">2021-11-09</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyngemose Parkvej 28A</t>
+          <t xml:space="preserve">Kagsåkollegiet 66</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -7176,20 +7176,20 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2098038</t>
+          <t xml:space="preserve">711938, 8777432</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J96">
-        <v>3669</v>
+        <v>672</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t xml:space="preserve">200054667</t>
+          <t xml:space="preserve">200056559</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -7199,7 +7199,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-11-09</t>
+          <t xml:space="preserve">2022-01-10</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kagsåkollegiet 66</t>
+          <t xml:space="preserve">Kagsåkollegiet 90</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -7256,15 +7256,15 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J97">
-        <v>672</v>
+        <v>448</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t xml:space="preserve">200056559</t>
+          <t xml:space="preserve">200056555</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kagsåkollegiet 90</t>
+          <t xml:space="preserve">Kellersvej 3</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -7326,20 +7326,20 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">711938, 8777432</t>
+          <t xml:space="preserve">8777413</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J98">
-        <v>448</v>
+        <v>1866</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t xml:space="preserve">200056555</t>
+          <t xml:space="preserve">200057567</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -7349,7 +7349,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-01-10</t>
+          <t xml:space="preserve">2022-02-21</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kellersvej 3</t>
+          <t xml:space="preserve">Kellersvej 7</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -7406,20 +7406,20 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J99">
-        <v>1866</v>
+        <v>222</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t xml:space="preserve">200057570</t>
+          <t xml:space="preserve">200057568</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Henrik Larsen Rådgivende Ingeniørfirma A/S</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kellersvej 7</t>
+          <t xml:space="preserve">Høje Gladsaxe Torv 4</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -7476,30 +7476,30 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777413</t>
+          <t xml:space="preserve">8777389</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J100">
-        <v>222</v>
+        <v>3306</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t xml:space="preserve">200057570</t>
+          <t xml:space="preserve">200057719</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Grontmij A/S</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-02-21</t>
+          <t xml:space="preserve">2022-02-27</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7541,17 +7541,17 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høje Gladsaxe Torv 4</t>
+          <t xml:space="preserve">Værebrovej 156</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2880</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777389</t>
+          <t xml:space="preserve">2088846</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -7560,11 +7560,11 @@
         </is>
       </c>
       <c r="J101">
-        <v>3306</v>
+        <v>1409</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t xml:space="preserve">200057719</t>
+          <t xml:space="preserve">200057710</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -7631,11 +7631,11 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J102">
-        <v>1409</v>
+        <v>10147</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
@@ -7706,15 +7706,15 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J103">
-        <v>10147</v>
+        <v>1955</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t xml:space="preserve">200057710</t>
+          <t xml:space="preserve">200057708</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Værebrovej 156</t>
+          <t xml:space="preserve">Værebrovej 158A</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -7781,15 +7781,15 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J104">
-        <v>1955</v>
+        <v>730</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t xml:space="preserve">200057708</t>
+          <t xml:space="preserve">200057709</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -7841,30 +7841,30 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Værebrovej 158A</t>
+          <t xml:space="preserve">Wergelands Alle 2</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2880</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2088846</t>
+          <t xml:space="preserve">2009784</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J105">
-        <v>730</v>
+        <v>9046</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t xml:space="preserve">200057709</t>
+          <t xml:space="preserve">200057707</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wergelands Alle 2</t>
+          <t xml:space="preserve">Frødings Alle 3</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -7926,7 +7926,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2009784</t>
+          <t xml:space="preserve">212352, 212353, 212354, 212355, 212357, 212358, 212356, 212359</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -7935,21 +7935,21 @@
         </is>
       </c>
       <c r="J106">
-        <v>9046</v>
+        <v>360</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t xml:space="preserve">200057707</t>
+          <t xml:space="preserve">311084106</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grontmij A/S</t>
+          <t xml:space="preserve">Bang &amp; Beenfeldt A/S</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-02-27</t>
+          <t xml:space="preserve">2024-11-19</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frødings Alle 3</t>
+          <t xml:space="preserve">Oktobervej 125</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">212352, 212353, 212354, 212355, 212357, 212358, 212356, 212359</t>
+          <t xml:space="preserve">711971, 2099390</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -8010,21 +8010,21 @@
         </is>
       </c>
       <c r="J107">
-        <v>360</v>
+        <v>104</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311084106</t>
+          <t xml:space="preserve">311091461</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bang &amp; Beenfeldt A/S</t>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-11-19</t>
+          <t xml:space="preserve">2025-01-18</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oktobervej 125</t>
+          <t xml:space="preserve">Oktobervej 127</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -8076,7 +8076,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">711971, 2099390</t>
+          <t xml:space="preserve">711972, 2099389</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -8089,7 +8089,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311091461</t>
+          <t xml:space="preserve">311185369</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -8099,7 +8099,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-01-18</t>
+          <t xml:space="preserve">2026-06-23</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8141,17 +8141,17 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oktobervej 127</t>
+          <t xml:space="preserve">Bagsværd Hovedgade 177</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2880</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">711972, 2099389</t>
+          <t xml:space="preserve">2085263</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -8160,31 +8160,31 @@
         </is>
       </c>
       <c r="J109">
-        <v>104</v>
+        <v>148</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311185369</t>
+          <t xml:space="preserve">311229356</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve">Norconsult A/S</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-23</t>
+          <t xml:space="preserve">2027-02-20</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -8216,17 +8216,17 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bagsværd Hovedgade 177</t>
+          <t xml:space="preserve">Nordvad 9</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2880</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2085263</t>
+          <t xml:space="preserve">2012604</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -8235,21 +8235,21 @@
         </is>
       </c>
       <c r="J110">
-        <v>148</v>
+        <v>7984</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311229356</t>
+          <t xml:space="preserve">311230939</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norconsult A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-20</t>
+          <t xml:space="preserve">2027-02-27</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8291,17 +8291,17 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordvad 9</t>
+          <t xml:space="preserve">Bagsværd Møllevej 3</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2012604</t>
+          <t xml:space="preserve">2089300</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -8310,21 +8310,21 @@
         </is>
       </c>
       <c r="J111">
-        <v>7984</v>
+        <v>1625</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230939</t>
+          <t xml:space="preserve">311242205</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-27</t>
+          <t xml:space="preserve">2027-04-21</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8366,40 +8366,40 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bagsværd Møllevej 3</t>
+          <t xml:space="preserve">Dynamovej 6</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2089300</t>
+          <t xml:space="preserve">711982, 2099475</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J112">
-        <v>1625</v>
+        <v>551</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311242205</t>
+          <t xml:space="preserve">311356775</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-21</t>
+          <t xml:space="preserve">2029-01-28</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dynamovej 6</t>
+          <t xml:space="preserve">Pilegårdsvej 100</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -8451,30 +8451,30 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">711982, 2099475</t>
+          <t xml:space="preserve">2098100</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J113">
-        <v>551</v>
+        <v>667</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311356775</t>
+          <t xml:space="preserve">311365532</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-01-28</t>
+          <t xml:space="preserve">2029-03-19</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8511,45 +8511,45 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">159</t>
+          <t xml:space="preserve">151</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pilegårdsvej 100</t>
+          <t xml:space="preserve">Damsagervej 9</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">3500</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2098100</t>
+          <t xml:space="preserve">2109413, 100724820</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J114">
-        <v>667</v>
+        <v>1554</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311365532</t>
+          <t xml:space="preserve">311403334</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
+          <t xml:space="preserve">CB Group af 2017 ApS</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-03-19</t>
+          <t xml:space="preserve">2029-10-11</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8586,45 +8586,45 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t xml:space="preserve">151</t>
+          <t xml:space="preserve">159</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Damsagervej 9</t>
+          <t xml:space="preserve">Bagsværd Hovedgade 50</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">3500</t>
+          <t xml:space="preserve">2880</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2109413, 100724820</t>
+          <t xml:space="preserve">7101570</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J115">
-        <v>1554</v>
+        <v>1114</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311403334</t>
+          <t xml:space="preserve">311408325</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t xml:space="preserve">CB Group af 2017 ApS</t>
+          <t xml:space="preserve">Danakon a/s</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-10-11</t>
+          <t xml:space="preserve">2029-11-11</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8666,17 +8666,17 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bagsværd Hovedgade 50</t>
+          <t xml:space="preserve">Kildebakken 30</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2880</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">7101570</t>
+          <t xml:space="preserve">2013088</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -8685,11 +8685,11 @@
         </is>
       </c>
       <c r="J116">
-        <v>1114</v>
+        <v>812</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311408325</t>
+          <t xml:space="preserve">311408323</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildebakken 30</t>
+          <t xml:space="preserve">Kildebakken 40</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -8751,7 +8751,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2013088</t>
+          <t xml:space="preserve">2013102</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -8760,11 +8760,11 @@
         </is>
       </c>
       <c r="J117">
-        <v>812</v>
+        <v>275</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311408323</t>
+          <t xml:space="preserve">311408322</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildebakken 40</t>
+          <t xml:space="preserve">Kildebakken 44</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2013102</t>
+          <t xml:space="preserve">2013089</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -8835,11 +8835,11 @@
         </is>
       </c>
       <c r="J118">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311408322</t>
+          <t xml:space="preserve">311408321</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -8891,17 +8891,17 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildebakken 44</t>
+          <t xml:space="preserve">Vadstrupvej 20A</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2880</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2013089</t>
+          <t xml:space="preserve">2085304</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -8910,11 +8910,11 @@
         </is>
       </c>
       <c r="J119">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311408321</t>
+          <t xml:space="preserve">311408324</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vadstrupvej 20A</t>
+          <t xml:space="preserve">Bagsværd Hovedgade 86</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2085304</t>
+          <t xml:space="preserve">2086993</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -8985,21 +8985,21 @@
         </is>
       </c>
       <c r="J120">
-        <v>272</v>
+        <v>1194</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311408324</t>
+          <t xml:space="preserve">311415734</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Danakon a/s</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-11-11</t>
+          <t xml:space="preserve">2030-01-03</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -9056,11 +9056,11 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J121">
-        <v>1194</v>
+        <v>499</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
@@ -9116,7 +9116,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bagsværd Hovedgade 86</t>
+          <t xml:space="preserve">Værebrovej 158</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -9126,20 +9126,20 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2086993</t>
+          <t xml:space="preserve">2088846</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J122">
-        <v>499</v>
+        <v>2225</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311415734</t>
+          <t xml:space="preserve">311415889</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-03</t>
+          <t xml:space="preserve">2030-01-06</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Værebrovej 158</t>
+          <t xml:space="preserve">Bagsværddal 15</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -9201,30 +9201,30 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2088846</t>
+          <t xml:space="preserve">2084680</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J123">
-        <v>2225</v>
+        <v>760</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311415889</t>
+          <t xml:space="preserve">311417120</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">Danakon a/s</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-06</t>
+          <t xml:space="preserve">2030-01-14</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9266,17 +9266,17 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bagsværddal 15</t>
+          <t xml:space="preserve">Carl Blochs Alle 7</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2880</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2084680</t>
+          <t xml:space="preserve">2014070</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -9285,11 +9285,11 @@
         </is>
       </c>
       <c r="J124">
-        <v>760</v>
+        <v>782</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311417120</t>
+          <t xml:space="preserve">311417092</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carl Blochs Alle 7</t>
+          <t xml:space="preserve">Carl Møllers Alle 1</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2014070</t>
+          <t xml:space="preserve">2014490</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -9360,11 +9360,11 @@
         </is>
       </c>
       <c r="J125">
-        <v>782</v>
+        <v>2207</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311417092</t>
+          <t xml:space="preserve">311417115</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -9416,30 +9416,30 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carl Møllers Alle 1</t>
+          <t xml:space="preserve">Elledalen 8</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2014490</t>
+          <t xml:space="preserve">2018039</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J126">
-        <v>2207</v>
+        <v>460</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311417115</t>
+          <t xml:space="preserve">311417148</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -9491,30 +9491,30 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elledalen 8</t>
+          <t xml:space="preserve">Gladsaxe Møllevej 65</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2018039</t>
+          <t xml:space="preserve">2017046</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J127">
-        <v>460</v>
+        <v>329</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311417148</t>
+          <t xml:space="preserve">311417095</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gladsaxe Møllevej 65</t>
+          <t xml:space="preserve">Kagsåvej 93</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -9576,7 +9576,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2017046</t>
+          <t xml:space="preserve">222534</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -9585,11 +9585,11 @@
         </is>
       </c>
       <c r="J128">
-        <v>329</v>
+        <v>316</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311417095</t>
+          <t xml:space="preserve">311417100</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -9641,7 +9641,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kagsåvej 93</t>
+          <t xml:space="preserve">Kagsåvej 97</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -9651,12 +9651,12 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">222534</t>
+          <t xml:space="preserve">222533, 222534</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J129">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kagsåvej 97</t>
+          <t xml:space="preserve">Kildebakkegårds Alle 171</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -9726,20 +9726,20 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">222533, 222534</t>
+          <t xml:space="preserve">2013620</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J130">
-        <v>316</v>
+        <v>1400</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311417100</t>
+          <t xml:space="preserve">311417096</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildebakkegårds Alle 171</t>
+          <t xml:space="preserve">Mørkhøjvej 154</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -9801,20 +9801,20 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2013620</t>
+          <t xml:space="preserve">7295209</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J131">
-        <v>1400</v>
+        <v>720</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311417096</t>
+          <t xml:space="preserve">311417091</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -9866,7 +9866,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mørkhøjvej 154</t>
+          <t xml:space="preserve">Signalvej 95</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -9876,7 +9876,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">7295209</t>
+          <t xml:space="preserve">9883414</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -9885,11 +9885,11 @@
         </is>
       </c>
       <c r="J132">
-        <v>720</v>
+        <v>4672</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311417091</t>
+          <t xml:space="preserve">311417114</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Signalvej 95</t>
+          <t xml:space="preserve">Søborg Hovedgade 198</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -9951,7 +9951,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">9883414</t>
+          <t xml:space="preserve">220694, 220695</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -9960,16 +9960,16 @@
         </is>
       </c>
       <c r="J133">
-        <v>4672</v>
+        <v>1924</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311417114</t>
+          <t xml:space="preserve">311417101</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Danakon a/s</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -10016,17 +10016,17 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søborg Hovedgade 198</t>
+          <t xml:space="preserve">Taxvej 27</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2880</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">220694, 220695</t>
+          <t xml:space="preserve">2085363</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -10035,16 +10035,16 @@
         </is>
       </c>
       <c r="J134">
-        <v>1924</v>
+        <v>1927</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311417101</t>
+          <t xml:space="preserve">311417112</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Danakon a/s</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -10091,40 +10091,40 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taxvej 27</t>
+          <t xml:space="preserve">Kong Hans Alle 43</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2880</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2085363</t>
+          <t xml:space="preserve">2012391</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J135">
-        <v>1927</v>
+        <v>471</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311417112</t>
+          <t xml:space="preserve">311418137</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Danakon a/s</t>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-14</t>
+          <t xml:space="preserve">2030-01-21</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -10166,7 +10166,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kong Hans Alle 43</t>
+          <t xml:space="preserve">Buddinge Hovedgade 111</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -10176,30 +10176,30 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2012391</t>
+          <t xml:space="preserve">2012253</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J136">
-        <v>471</v>
+        <v>484</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311418137</t>
+          <t xml:space="preserve">311418880</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">Danakon a/s</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-21</t>
+          <t xml:space="preserve">2030-01-24</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buddinge Hovedgade 111</t>
+          <t xml:space="preserve">Valdemars Alle 81</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -10251,20 +10251,20 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2012253</t>
+          <t xml:space="preserve">8777413</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="J137">
-        <v>484</v>
+        <v>1680</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311418880</t>
+          <t xml:space="preserve">311418879</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -10316,7 +10316,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valdemars Alle 81</t>
+          <t xml:space="preserve">Højmarksvej 24</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -10326,30 +10326,30 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777413</t>
+          <t xml:space="preserve">2010230</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J138">
-        <v>1680</v>
+        <v>639</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311418879</t>
+          <t xml:space="preserve">311423941</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Danakon a/s</t>
+          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-24</t>
+          <t xml:space="preserve">2030-02-21</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højmarksvej 24</t>
+          <t xml:space="preserve">Tobaksvejen 24</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -10401,7 +10401,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2010230</t>
+          <t xml:space="preserve">2018588</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -10410,11 +10410,11 @@
         </is>
       </c>
       <c r="J139">
-        <v>639</v>
+        <v>895</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311423941</t>
+          <t xml:space="preserve">311423940</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -10466,7 +10466,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tobaksvejen 24</t>
+          <t xml:space="preserve">Carl Møllers Alle 7</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -10476,7 +10476,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2018588</t>
+          <t xml:space="preserve">2011266</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -10485,11 +10485,11 @@
         </is>
       </c>
       <c r="J140">
-        <v>895</v>
+        <v>482</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311423940</t>
+          <t xml:space="preserve">311424125</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -10499,7 +10499,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-02-21</t>
+          <t xml:space="preserve">2030-02-24</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carl Møllers Alle 7</t>
+          <t xml:space="preserve">Christianehøj 164</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2011266</t>
+          <t xml:space="preserve">2013432</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -10560,11 +10560,11 @@
         </is>
       </c>
       <c r="J141">
-        <v>482</v>
+        <v>507</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311424125</t>
+          <t xml:space="preserve">311424132</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -10616,7 +10616,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christianehøj 164</t>
+          <t xml:space="preserve">Lauggårds Alle 15</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -10626,7 +10626,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2013432</t>
+          <t xml:space="preserve">2010032</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -10635,11 +10635,11 @@
         </is>
       </c>
       <c r="J142">
-        <v>507</v>
+        <v>731</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311424132</t>
+          <t xml:space="preserve">311424128</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -10691,7 +10691,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lauggårds Alle 15</t>
+          <t xml:space="preserve">Gladsaxevej 200</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -10701,7 +10701,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2010032</t>
+          <t xml:space="preserve">9123186</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -10710,21 +10710,21 @@
         </is>
       </c>
       <c r="J143">
-        <v>731</v>
+        <v>6329</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311424128</t>
+          <t xml:space="preserve">311425249</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-02-24</t>
+          <t xml:space="preserve">2030-02-28</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10766,7 +10766,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gladsaxevej 200</t>
+          <t xml:space="preserve">Gladsaxevej 200C</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -10781,11 +10781,11 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J144">
-        <v>6329</v>
+        <v>764</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gladsaxevej 200C</t>
+          <t xml:space="preserve">Gladsaxevej 204</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -10856,11 +10856,11 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J145">
-        <v>764</v>
+        <v>614</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
@@ -10916,7 +10916,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gladsaxevej 204</t>
+          <t xml:space="preserve">Isbanevej 3</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -10931,11 +10931,11 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J146">
-        <v>614</v>
+        <v>4930</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isbanevej 3</t>
+          <t xml:space="preserve">Vandtårnsvej 57</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -11006,11 +11006,11 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J147">
-        <v>4930</v>
+        <v>2404</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
@@ -11066,7 +11066,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vandtårnsvej 57</t>
+          <t xml:space="preserve">Alsikemarken 13</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -11076,30 +11076,30 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">9123186</t>
+          <t xml:space="preserve">2016721</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J148">
-        <v>2404</v>
+        <v>754</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311425249</t>
+          <t xml:space="preserve">311427843</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-02-28</t>
+          <t xml:space="preserve">2030-03-13</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -11141,7 +11141,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alsikemarken 13</t>
+          <t xml:space="preserve">Solnavej 74B</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -11151,7 +11151,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2016721</t>
+          <t xml:space="preserve">2013032</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -11160,11 +11160,11 @@
         </is>
       </c>
       <c r="J149">
-        <v>754</v>
+        <v>634</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311427843</t>
+          <t xml:space="preserve">311427844</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -11216,7 +11216,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solnavej 74B</t>
+          <t xml:space="preserve">Søborghus Alle 23</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -11226,7 +11226,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2013032</t>
+          <t xml:space="preserve">2009443</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -11235,11 +11235,11 @@
         </is>
       </c>
       <c r="J150">
-        <v>634</v>
+        <v>507</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311427844</t>
+          <t xml:space="preserve">311427845</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -11291,7 +11291,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søborghus Alle 23</t>
+          <t xml:space="preserve">Vandtårnsvej 55</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -11301,30 +11301,30 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2009443</t>
+          <t xml:space="preserve">9123186</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J151">
-        <v>507</v>
+        <v>7550</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311427845</t>
+          <t xml:space="preserve">311428045</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-03-13</t>
+          <t xml:space="preserve">2030-03-14</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11381,15 +11381,15 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J152">
-        <v>7550</v>
+        <v>2678</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311428045</t>
+          <t xml:space="preserve">311428043</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -11441,7 +11441,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vandtårnsvej 55</t>
+          <t xml:space="preserve">Dickens Alle 7</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -11451,30 +11451,30 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">9123186</t>
+          <t xml:space="preserve">2013725</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J153">
-        <v>2678</v>
+        <v>471</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311428043</t>
+          <t xml:space="preserve">311428180</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-03-14</t>
+          <t xml:space="preserve">2030-03-16</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11516,7 +11516,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dickens Alle 7</t>
+          <t xml:space="preserve">Vandtårnsvej 59</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -11526,7 +11526,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2013725</t>
+          <t xml:space="preserve">9689080</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -11535,21 +11535,21 @@
         </is>
       </c>
       <c r="J154">
-        <v>471</v>
+        <v>4992</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311428180</t>
+          <t xml:space="preserve">311433225</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-03-16</t>
+          <t xml:space="preserve">2030-04-17</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11591,40 +11591,40 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vandtårnsvej 59</t>
+          <t xml:space="preserve">Taxvej 17</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2880</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">9689080</t>
+          <t xml:space="preserve">2085261</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J155">
-        <v>4992</v>
+        <v>382</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311433225</t>
+          <t xml:space="preserve">311435810</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-04-17</t>
+          <t xml:space="preserve">2030-05-04</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11666,30 +11666,30 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taxvej 17</t>
+          <t xml:space="preserve">Vadgårdsvej 9</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2880</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2085261</t>
+          <t xml:space="preserve">1300247</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J156">
-        <v>382</v>
+        <v>514</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311435810</t>
+          <t xml:space="preserve">311435811</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -11741,17 +11741,17 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vadgårdsvej 9</t>
+          <t xml:space="preserve">Amundsensvej 13</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">1300247</t>
+          <t xml:space="preserve">2087370</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -11760,11 +11760,11 @@
         </is>
       </c>
       <c r="J157">
-        <v>514</v>
+        <v>385</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311435811</t>
+          <t xml:space="preserve">311437248</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-05-04</t>
+          <t xml:space="preserve">2030-05-12</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11816,30 +11816,30 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amundsensvej 13</t>
+          <t xml:space="preserve">Dickens Alle 13</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2087370</t>
+          <t xml:space="preserve">8042705</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J158">
-        <v>385</v>
+        <v>579</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311437248</t>
+          <t xml:space="preserve">311437243</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -11891,30 +11891,30 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dickens Alle 13</t>
+          <t xml:space="preserve">Krakasvej 1</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">8042705</t>
+          <t xml:space="preserve">2084925</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J159">
-        <v>579</v>
+        <v>795</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311437243</t>
+          <t xml:space="preserve">311437240</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krakasvej 1</t>
+          <t xml:space="preserve">Krakasvej 3</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -11981,15 +11981,15 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J160">
-        <v>795</v>
+        <v>586</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311437240</t>
+          <t xml:space="preserve">311437242</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -12041,30 +12041,30 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krakasvej 3</t>
+          <t xml:space="preserve">Oktobervej 20</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2084925</t>
+          <t xml:space="preserve">2099473</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J161">
-        <v>586</v>
+        <v>1003</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311437242</t>
+          <t xml:space="preserve">311437244</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -12116,7 +12116,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oktobervej 20</t>
+          <t xml:space="preserve">Mørkhøjvej 330</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -12126,20 +12126,20 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2099473</t>
+          <t xml:space="preserve">7295209</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J162">
-        <v>1003</v>
+        <v>602</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311437244</t>
+          <t xml:space="preserve">311440303</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -12149,7 +12149,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-05-12</t>
+          <t xml:space="preserve">2030-05-28</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -12191,7 +12191,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mørkhøjvej 330</t>
+          <t xml:space="preserve">Pilegårdsvej 1</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -12201,20 +12201,20 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">7295209</t>
+          <t xml:space="preserve">1302084</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J163">
-        <v>602</v>
+        <v>771</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311440303</t>
+          <t xml:space="preserve">311440635</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -12224,7 +12224,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-05-28</t>
+          <t xml:space="preserve">2030-05-29</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -12266,17 +12266,17 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pilegårdsvej 1</t>
+          <t xml:space="preserve">Gammelmosevej 306</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2880</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">1302084</t>
+          <t xml:space="preserve">2086546</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -12285,11 +12285,11 @@
         </is>
       </c>
       <c r="J164">
-        <v>771</v>
+        <v>202</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311440635</t>
+          <t xml:space="preserve">311442581</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -12299,7 +12299,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-05-29</t>
+          <t xml:space="preserve">2030-06-10</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -12356,11 +12356,11 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J165">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
@@ -12431,11 +12431,11 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J166">
-        <v>208</v>
+        <v>80</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
@@ -12491,7 +12491,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammelmosevej 306</t>
+          <t xml:space="preserve">Skovdiget 8</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -12501,20 +12501,20 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2086546</t>
+          <t xml:space="preserve">2089220</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J167">
-        <v>80</v>
+        <v>504</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311442581</t>
+          <t xml:space="preserve">311442579</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovdiget 8</t>
+          <t xml:space="preserve">Taxvej 19</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -12576,7 +12576,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2089220</t>
+          <t xml:space="preserve">8045419</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -12585,11 +12585,11 @@
         </is>
       </c>
       <c r="J168">
-        <v>504</v>
+        <v>599</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311442579</t>
+          <t xml:space="preserve">311442578</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -12641,17 +12641,17 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taxvej 19</t>
+          <t xml:space="preserve">Esberns Alle 15</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2880</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">8045419</t>
+          <t xml:space="preserve">1300237</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -12660,11 +12660,11 @@
         </is>
       </c>
       <c r="J169">
-        <v>599</v>
+        <v>937</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311442578</t>
+          <t xml:space="preserve">311443511</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -12674,7 +12674,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-06-10</t>
+          <t xml:space="preserve">2030-06-15</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12716,7 +12716,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Esberns Alle 15</t>
+          <t xml:space="preserve">Gyngemose Parkvej 30</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -12726,7 +12726,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">1300237</t>
+          <t xml:space="preserve">8777683</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -12735,11 +12735,11 @@
         </is>
       </c>
       <c r="J170">
-        <v>937</v>
+        <v>382</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311443511</t>
+          <t xml:space="preserve">311443510</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyngemose Parkvej 30</t>
+          <t xml:space="preserve">Gyngemose Parkvej 32</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -12806,15 +12806,15 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J171">
-        <v>382</v>
+        <v>416</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311443510</t>
+          <t xml:space="preserve">311443509</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -12866,7 +12866,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyngemose Parkvej 32</t>
+          <t xml:space="preserve">Kildebakkegårds Alle 166</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -12876,20 +12876,20 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777683</t>
+          <t xml:space="preserve">2013279</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J172">
-        <v>416</v>
+        <v>488</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311443509</t>
+          <t xml:space="preserve">311443524</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -12941,7 +12941,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildebakkegårds Alle 166</t>
+          <t xml:space="preserve">Provst Bentzons Vej 7</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -12951,7 +12951,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2013279</t>
+          <t xml:space="preserve">2014951</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -12960,11 +12960,11 @@
         </is>
       </c>
       <c r="J173">
-        <v>488</v>
+        <v>549</v>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311443524</t>
+          <t xml:space="preserve">311443507</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provst Bentzons Vej 7</t>
+          <t xml:space="preserve">Slotsparken 31</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2880</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2014951</t>
+          <t xml:space="preserve">8007543</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -13035,11 +13035,11 @@
         </is>
       </c>
       <c r="J174">
-        <v>549</v>
+        <v>572</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311443507</t>
+          <t xml:space="preserve">311443504</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -13091,7 +13091,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slotsparken 31</t>
+          <t xml:space="preserve">Ibsvej 3</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -13101,7 +13101,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">8007543</t>
+          <t xml:space="preserve">8777661</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -13110,11 +13110,11 @@
         </is>
       </c>
       <c r="J175">
-        <v>572</v>
+        <v>1110</v>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311443504</t>
+          <t xml:space="preserve">311447153</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -13124,7 +13124,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-06-15</t>
+          <t xml:space="preserve">2030-07-01</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -13166,17 +13166,17 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ibsvej 3</t>
+          <t xml:space="preserve">Gladsaxevej 9</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2880</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777661</t>
+          <t xml:space="preserve">10228151</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -13185,11 +13185,11 @@
         </is>
       </c>
       <c r="J176">
-        <v>1110</v>
+        <v>749</v>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311447153</t>
+          <t xml:space="preserve">311451637</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -13199,7 +13199,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-07-01</t>
+          <t xml:space="preserve">2030-07-29</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -13241,7 +13241,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gladsaxevej 9</t>
+          <t xml:space="preserve">Ilbjerg Alle 38A</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -13251,7 +13251,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">10228151</t>
+          <t xml:space="preserve">2098527</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -13260,21 +13260,21 @@
         </is>
       </c>
       <c r="J177">
-        <v>749</v>
+        <v>627</v>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311451637</t>
+          <t xml:space="preserve">311492842</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-07-29</t>
+          <t xml:space="preserve">2031-02-04</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -13316,17 +13316,17 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ilbjerg Alle 38A</t>
+          <t xml:space="preserve">Elledalen 6</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2098527</t>
+          <t xml:space="preserve">2018039</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -13335,11 +13335,11 @@
         </is>
       </c>
       <c r="J178">
-        <v>627</v>
+        <v>263</v>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311492842</t>
+          <t xml:space="preserve">311493115</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -13349,7 +13349,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-04</t>
+          <t xml:space="preserve">2031-02-05</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -13391,7 +13391,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elledalen 6</t>
+          <t xml:space="preserve">Triumfvej 1</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -13401,7 +13401,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2018039</t>
+          <t xml:space="preserve">2086057</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -13410,11 +13410,11 @@
         </is>
       </c>
       <c r="J179">
-        <v>263</v>
+        <v>6769</v>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311493115</t>
+          <t xml:space="preserve">311494342</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-05</t>
+          <t xml:space="preserve">2031-02-10</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13466,30 +13466,30 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Triumfvej 1</t>
+          <t xml:space="preserve">Gladsaxevej 17</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2086057</t>
+          <t xml:space="preserve">10228151</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J180">
-        <v>6769</v>
+        <v>326</v>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494342</t>
+          <t xml:space="preserve">311494603</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -13499,7 +13499,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-10</t>
+          <t xml:space="preserve">2031-02-11</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13541,7 +13541,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gladsaxevej 17</t>
+          <t xml:space="preserve">Transformervej 5</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -13551,20 +13551,20 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">10228151</t>
+          <t xml:space="preserve">8777493</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J181">
-        <v>326</v>
+        <v>810</v>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494603</t>
+          <t xml:space="preserve">311494601</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -13616,7 +13616,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transformervej 5</t>
+          <t xml:space="preserve">Ilbjerg Alle 38B</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -13626,20 +13626,20 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777493</t>
+          <t xml:space="preserve">2098527</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J182">
-        <v>810</v>
+        <v>547</v>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494601</t>
+          <t xml:space="preserve">311499350</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -13649,7 +13649,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-11</t>
+          <t xml:space="preserve">2031-03-01</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13691,7 +13691,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ilbjerg Alle 38B</t>
+          <t xml:space="preserve">Frødings Alle 4</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -13701,20 +13701,20 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">2098527</t>
+          <t xml:space="preserve">2009889</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J183">
-        <v>547</v>
+        <v>204</v>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311499350</t>
+          <t xml:space="preserve">311505510</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -13724,7 +13724,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-01</t>
+          <t xml:space="preserve">2031-03-22</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13781,15 +13781,15 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J184">
-        <v>204</v>
+        <v>336</v>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311505510</t>
+          <t xml:space="preserve">311505511</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -13841,7 +13841,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frødings Alle 4</t>
+          <t xml:space="preserve">Klausdalsbrovej 195</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -13851,20 +13851,20 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2009889</t>
+          <t xml:space="preserve">2016076</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J185">
-        <v>336</v>
+        <v>219</v>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311505511</t>
+          <t xml:space="preserve">311505525</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -13931,15 +13931,15 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J186">
-        <v>219</v>
+        <v>574</v>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311505525</t>
+          <t xml:space="preserve">311505526</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -13991,7 +13991,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klausdalsbrovej 195</t>
+          <t xml:space="preserve">Gladsaxevej 198</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -14001,20 +14001,20 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2016076</t>
+          <t xml:space="preserve">2011846</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J187">
-        <v>574</v>
+        <v>9180</v>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311505526</t>
+          <t xml:space="preserve">311508956</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -14024,7 +14024,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-22</t>
+          <t xml:space="preserve">2031-03-31</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -14081,15 +14081,15 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J188">
-        <v>9180</v>
+        <v>95</v>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311508956</t>
+          <t xml:space="preserve">311508957</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -14156,15 +14156,15 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J189">
-        <v>95</v>
+        <v>502</v>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311508957</t>
+          <t xml:space="preserve">311508958</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -14231,15 +14231,15 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J190">
-        <v>502</v>
+        <v>1366</v>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311508958</t>
+          <t xml:space="preserve">311508959</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -14291,7 +14291,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gladsaxevej 198</t>
+          <t xml:space="preserve">Gladsaxevej 198A</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -14306,15 +14306,15 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J191">
-        <v>1366</v>
+        <v>224</v>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311508959</t>
+          <t xml:space="preserve">311508960</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -14366,30 +14366,30 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gladsaxevej 198A</t>
+          <t xml:space="preserve">Nybrovej 321</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2011846</t>
+          <t xml:space="preserve">7101580</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J192">
-        <v>224</v>
+        <v>594</v>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311508960</t>
+          <t xml:space="preserve">311510225</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -14399,7 +14399,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-31</t>
+          <t xml:space="preserve">2031-04-06</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -14441,7 +14441,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nybrovej 321</t>
+          <t xml:space="preserve">Nybrovej 331</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -14456,11 +14456,11 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J193">
-        <v>594</v>
+        <v>293</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
@@ -14516,7 +14516,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nybrovej 331</t>
+          <t xml:space="preserve">Nybrovej 333</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -14531,11 +14531,11 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J194">
-        <v>293</v>
+        <v>1862</v>
       </c>
       <c r="K194" t="inlineStr">
         <is>
@@ -14591,30 +14591,30 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nybrovej 333</t>
+          <t xml:space="preserve">Slotsparken 30</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2880</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">7101580</t>
+          <t xml:space="preserve">2087930</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J195">
-        <v>1862</v>
+        <v>667</v>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311510225</t>
+          <t xml:space="preserve">311510221</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -14666,17 +14666,17 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slotsparken 30</t>
+          <t xml:space="preserve">Bagsværdvej 138A</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t xml:space="preserve">2880</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve">2087930</t>
+          <t xml:space="preserve">9937922</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -14685,11 +14685,11 @@
         </is>
       </c>
       <c r="J196">
-        <v>667</v>
+        <v>180</v>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311510221</t>
+          <t xml:space="preserve">311513436</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -14699,7 +14699,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-06</t>
+          <t xml:space="preserve">2031-04-19</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14741,7 +14741,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bagsværdvej 138A</t>
+          <t xml:space="preserve">Bagsværdvej 138B</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -14756,7 +14756,7 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J197">
@@ -14816,7 +14816,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bagsværdvej 138B</t>
+          <t xml:space="preserve">Gammelmosevej 51A</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -14826,20 +14826,20 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">9937922</t>
+          <t xml:space="preserve">8777413</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="J198">
-        <v>180</v>
+        <v>1646</v>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t xml:space="preserve">311513436</t>
+          <t xml:space="preserve">311513471</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -14891,7 +14891,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammelmosevej 51A</t>
+          <t xml:space="preserve">Gammelmosevej 51E</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -14906,11 +14906,11 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="J199">
-        <v>1646</v>
+        <v>194</v>
       </c>
       <c r="K199" t="inlineStr">
         <is>
@@ -14966,7 +14966,7 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammelmosevej 51E</t>
+          <t xml:space="preserve">Gammelmosevej 51F</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -14981,7 +14981,7 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="J200">
@@ -15041,7 +15041,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammelmosevej 51F</t>
+          <t xml:space="preserve">Gammelmosevej 51G</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -15056,11 +15056,11 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="J201">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="K201" t="inlineStr">
         <is>
@@ -15116,7 +15116,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammelmosevej 51G</t>
+          <t xml:space="preserve">Tjele Alle 11</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -15126,30 +15126,30 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777413</t>
+          <t xml:space="preserve">2017700</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J202">
-        <v>180</v>
+        <v>628</v>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311513471</t>
+          <t xml:space="preserve">311513898</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Isolink ApS</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-19</t>
+          <t xml:space="preserve">2031-04-20</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -15191,7 +15191,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tjele Alle 11</t>
+          <t xml:space="preserve">Bagsværdvej 144A</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -15201,7 +15201,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t xml:space="preserve">2017700</t>
+          <t xml:space="preserve">8777610</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -15210,21 +15210,21 @@
         </is>
       </c>
       <c r="J203">
-        <v>628</v>
+        <v>706</v>
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t xml:space="preserve">311513898</t>
+          <t xml:space="preserve">311515445</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isolink ApS</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-20</t>
+          <t xml:space="preserve">2031-04-26</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -15266,30 +15266,30 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bagsværdvej 144A</t>
+          <t xml:space="preserve">Bagsværd Hovedgade 116</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2880</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777610</t>
+          <t xml:space="preserve">209314</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J204">
-        <v>706</v>
+        <v>406</v>
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t xml:space="preserve">311515445</t>
+          <t xml:space="preserve">311516729</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
@@ -15299,7 +15299,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-26</t>
+          <t xml:space="preserve">2031-04-29</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -15351,16 +15351,16 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve">209314</t>
+          <t xml:space="preserve">209704</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J205">
-        <v>406</v>
+        <v>1143</v>
       </c>
       <c r="K205" t="inlineStr">
         <is>
@@ -15416,7 +15416,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bagsværd Hovedgade 116</t>
+          <t xml:space="preserve">Bagsværd Hovedgade 53</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -15426,20 +15426,20 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t xml:space="preserve">209704</t>
+          <t xml:space="preserve">2088853</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J206">
-        <v>1143</v>
+        <v>215</v>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t xml:space="preserve">311516729</t>
+          <t xml:space="preserve">311518538</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
@@ -15449,7 +15449,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-29</t>
+          <t xml:space="preserve">2031-05-07</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -15491,7 +15491,7 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bagsværd Hovedgade 53</t>
+          <t xml:space="preserve">Skovalleen 38B</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
@@ -15501,7 +15501,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t xml:space="preserve">2088853</t>
+          <t xml:space="preserve">711983, 2088539</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -15510,11 +15510,11 @@
         </is>
       </c>
       <c r="J207">
-        <v>215</v>
+        <v>1272</v>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t xml:space="preserve">311518538</t>
+          <t xml:space="preserve">311523012</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -15524,7 +15524,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-07</t>
+          <t xml:space="preserve">2031-05-27</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -15566,7 +15566,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovalleen 38B</t>
+          <t xml:space="preserve">Skovdiget 1</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -15576,30 +15576,30 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t xml:space="preserve">711983, 2088539</t>
+          <t xml:space="preserve">711977, 2085091</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J208">
-        <v>1272</v>
+        <v>4665</v>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t xml:space="preserve">311523012</t>
+          <t xml:space="preserve">311525498</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-27</t>
+          <t xml:space="preserve">2031-06-04</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15641,7 +15641,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovdiget 1</t>
+          <t xml:space="preserve">Granvej 53</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -15651,30 +15651,30 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t xml:space="preserve">711977, 2085091</t>
+          <t xml:space="preserve">711916, 2085366</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J209">
-        <v>4665</v>
+        <v>2041</v>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t xml:space="preserve">311525498</t>
+          <t xml:space="preserve">311526998</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-04</t>
+          <t xml:space="preserve">2031-06-10</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15716,40 +15716,40 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Granvej 53</t>
+          <t xml:space="preserve">Vandtårnsvej 61</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t xml:space="preserve">2880</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t xml:space="preserve">711916, 2085366</t>
+          <t xml:space="preserve">9689138, 100531698</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J210">
-        <v>2041</v>
+        <v>1212</v>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t xml:space="preserve">311526998</t>
+          <t xml:space="preserve">311535541</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-10</t>
+          <t xml:space="preserve">2031-07-13</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15791,7 +15791,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vandtårnsvej 61</t>
+          <t xml:space="preserve">Høje Gladsaxe 1</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
@@ -15801,30 +15801,30 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t xml:space="preserve">9689138, 100531698</t>
+          <t xml:space="preserve">712006, 7151761</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J211">
-        <v>1212</v>
+        <v>18836</v>
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t xml:space="preserve">311535541</t>
+          <t xml:space="preserve">311582963</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">Domutech A/S</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-13</t>
+          <t xml:space="preserve">2032-03-07</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15866,7 +15866,7 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høje Gladsaxe 1</t>
+          <t xml:space="preserve">Høje Gladsaxe 106</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
@@ -15876,20 +15876,20 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t xml:space="preserve">712006, 7151761</t>
+          <t xml:space="preserve">712004, 7151669</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="J212">
-        <v>18836</v>
+        <v>3586</v>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582963</t>
+          <t xml:space="preserve">311582969</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -15941,7 +15941,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høje Gladsaxe 106</t>
+          <t xml:space="preserve">Høje Gladsaxe 11</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -15951,20 +15951,20 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t xml:space="preserve">712004, 7151669</t>
+          <t xml:space="preserve">712005, 7151760</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J213">
-        <v>3586</v>
+        <v>18836</v>
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582969</t>
+          <t xml:space="preserve">311582964</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -16016,7 +16016,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høje Gladsaxe 11</t>
+          <t xml:space="preserve">Høje Gladsaxe 116</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
@@ -16026,20 +16026,20 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t xml:space="preserve">712005, 7151760</t>
+          <t xml:space="preserve">712004, 7151669</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="J214">
-        <v>18836</v>
+        <v>4854</v>
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582964</t>
+          <t xml:space="preserve">311582969</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
@@ -16091,7 +16091,7 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høje Gladsaxe 116</t>
+          <t xml:space="preserve">Høje Gladsaxe 16</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -16101,20 +16101,20 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t xml:space="preserve">712004, 7151669</t>
+          <t xml:space="preserve">712006, 7151761</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J215">
-        <v>4854</v>
+        <v>6472</v>
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582969</t>
+          <t xml:space="preserve">311582963</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
@@ -16166,7 +16166,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høje Gladsaxe 16</t>
+          <t xml:space="preserve">Høje Gladsaxe 32</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
@@ -16181,11 +16181,11 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="J216">
-        <v>6472</v>
+        <v>4854</v>
       </c>
       <c r="K216" t="inlineStr">
         <is>
@@ -16241,7 +16241,7 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høje Gladsaxe 32</t>
+          <t xml:space="preserve">Høje Gladsaxe 4</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -16256,11 +16256,11 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J217">
-        <v>4854</v>
+        <v>4848</v>
       </c>
       <c r="K217" t="inlineStr">
         <is>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høje Gladsaxe 4</t>
+          <t xml:space="preserve">Høje Gladsaxe 44</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -16326,20 +16326,20 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t xml:space="preserve">712006, 7151761</t>
+          <t xml:space="preserve">712005, 7151760</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J218">
-        <v>4848</v>
+        <v>4854</v>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582963</t>
+          <t xml:space="preserve">311582964</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
@@ -16391,7 +16391,7 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høje Gladsaxe 44</t>
+          <t xml:space="preserve">Høje Gladsaxe 56</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -16406,7 +16406,7 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J219">
@@ -16466,7 +16466,7 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høje Gladsaxe 56</t>
+          <t xml:space="preserve">Høje Gladsaxe 68</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -16481,11 +16481,11 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J220">
-        <v>4854</v>
+        <v>6472</v>
       </c>
       <c r="K220" t="inlineStr">
         <is>
@@ -16541,7 +16541,7 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høje Gladsaxe 68</t>
+          <t xml:space="preserve">Høje Gladsaxe 84</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -16551,7 +16551,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t xml:space="preserve">712005, 7151760</t>
+          <t xml:space="preserve">712004, 7151669</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -16560,11 +16560,11 @@
         </is>
       </c>
       <c r="J221">
-        <v>6472</v>
+        <v>4854</v>
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582964</t>
+          <t xml:space="preserve">311582969</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
@@ -16616,7 +16616,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høje Gladsaxe 84</t>
+          <t xml:space="preserve">Høje Gladsaxe 96</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -16631,11 +16631,11 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="J222">
-        <v>4854</v>
+        <v>3075</v>
       </c>
       <c r="K222" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høje Gladsaxe 96</t>
+          <t xml:space="preserve">Transformervej 3</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -16701,30 +16701,30 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t xml:space="preserve">712004, 7151669</t>
+          <t xml:space="preserve">8777493</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J223">
-        <v>3075</v>
+        <v>1330</v>
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582969</t>
+          <t xml:space="preserve">311592665</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Domutech A/S</t>
+          <t xml:space="preserve">Rådgivende Ingeniør Ole Lentz ApS</t>
         </is>
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-07</t>
+          <t xml:space="preserve">2032-04-12</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16766,7 +16766,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transformervej 3</t>
+          <t xml:space="preserve">Høje Gladsaxe 21</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
@@ -16776,30 +16776,30 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777493</t>
+          <t xml:space="preserve">712004, 7151669</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J224">
-        <v>1330</v>
+        <v>18833</v>
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t xml:space="preserve">311592665</t>
+          <t xml:space="preserve">311594594</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådgivende Ingeniør Ole Lentz ApS</t>
+          <t xml:space="preserve">Domutech A/S</t>
         </is>
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-12</t>
+          <t xml:space="preserve">2032-04-22</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16841,7 +16841,7 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høje Gladsaxe 21</t>
+          <t xml:space="preserve">Klausdalsbrovej 197</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
@@ -16851,30 +16851,30 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t xml:space="preserve">712004, 7151669</t>
+          <t xml:space="preserve">2016076</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J225">
-        <v>18833</v>
+        <v>1175</v>
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t xml:space="preserve">311594599</t>
+          <t xml:space="preserve">311600348</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Domutech A/S</t>
+          <t xml:space="preserve">Rådgivende Ingeniør Ole Lentz ApS</t>
         </is>
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-22</t>
+          <t xml:space="preserve">2032-05-16</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16916,7 +16916,7 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klausdalsbrovej 197</t>
+          <t xml:space="preserve">Oktobervej 34</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
@@ -16926,30 +16926,30 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t xml:space="preserve">2016076</t>
+          <t xml:space="preserve">711914, 2099443</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J226">
-        <v>1175</v>
+        <v>112</v>
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t xml:space="preserve">311600348</t>
+          <t xml:space="preserve">311619815</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådgivende Ingeniør Ole Lentz ApS</t>
+          <t xml:space="preserve">Domutech A/S</t>
         </is>
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-16</t>
+          <t xml:space="preserve">2032-08-11</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16991,7 +16991,7 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oktobervej 34</t>
+          <t xml:space="preserve">Kellersvej 11</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
@@ -17001,30 +17001,30 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t xml:space="preserve">711914, 2099443</t>
+          <t xml:space="preserve">8777413</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">36</t>
         </is>
       </c>
       <c r="J227">
-        <v>112</v>
+        <v>900</v>
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t xml:space="preserve">311619815</t>
+          <t xml:space="preserve">311646459</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Domutech A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-11</t>
+          <t xml:space="preserve">2032-12-01</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -17066,7 +17066,7 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kellersvej 11</t>
+          <t xml:space="preserve">Kellersvej 13</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
@@ -17081,7 +17081,7 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="J228">
@@ -17089,7 +17089,7 @@
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t xml:space="preserve">311646459</t>
+          <t xml:space="preserve">311646460</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
@@ -17141,7 +17141,7 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kellersvej 13</t>
+          <t xml:space="preserve">Kellersvej 9</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
@@ -17156,15 +17156,15 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">34</t>
         </is>
       </c>
       <c r="J229">
-        <v>900</v>
+        <v>1006</v>
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t xml:space="preserve">311646460</t>
+          <t xml:space="preserve">311646450</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
@@ -17216,7 +17216,7 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kellersvej 9</t>
+          <t xml:space="preserve">Kellersvej 15</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
@@ -17231,15 +17231,15 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t xml:space="preserve">34</t>
+          <t xml:space="preserve">38</t>
         </is>
       </c>
       <c r="J230">
-        <v>1006</v>
+        <v>1003</v>
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t xml:space="preserve">311646450</t>
+          <t xml:space="preserve">311647803</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
@@ -17249,7 +17249,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-01</t>
+          <t xml:space="preserve">2032-12-08</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -17291,7 +17291,7 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kellersvej 15</t>
+          <t xml:space="preserve">Kellersvej 17</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
@@ -17306,7 +17306,7 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t xml:space="preserve">38</t>
+          <t xml:space="preserve">39</t>
         </is>
       </c>
       <c r="J231">
@@ -17314,7 +17314,7 @@
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t xml:space="preserve">311647803</t>
+          <t xml:space="preserve">311647802</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
@@ -17366,7 +17366,7 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kellersvej 17</t>
+          <t xml:space="preserve">Kellersvej 19</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
@@ -17381,15 +17381,15 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t xml:space="preserve">39</t>
+          <t xml:space="preserve">40</t>
         </is>
       </c>
       <c r="J232">
-        <v>1003</v>
+        <v>900</v>
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t xml:space="preserve">311647802</t>
+          <t xml:space="preserve">311647790</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
@@ -17441,7 +17441,7 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kellersvej 19</t>
+          <t xml:space="preserve">Høje Gladsaxe 31</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
@@ -17451,30 +17451,30 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777413</t>
+          <t xml:space="preserve">712003, 7151668</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t xml:space="preserve">40</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J233">
-        <v>900</v>
+        <v>18836</v>
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t xml:space="preserve">311647790</t>
+          <t xml:space="preserve">311651315</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">Domutech A/S</t>
         </is>
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-08</t>
+          <t xml:space="preserve">2032-12-22</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -17516,7 +17516,7 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høje Gladsaxe 31</t>
+          <t xml:space="preserve">Høje Gladsaxe 51</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
@@ -17531,11 +17531,11 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J234">
-        <v>18836</v>
+        <v>10498</v>
       </c>
       <c r="K234" t="inlineStr">
         <is>
@@ -17591,7 +17591,7 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høje Gladsaxe 51</t>
+          <t xml:space="preserve">Oktobervej 95</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
@@ -17601,20 +17601,20 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t xml:space="preserve">712003, 7151668</t>
+          <t xml:space="preserve">711965, 2099405</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J235">
-        <v>10498</v>
+        <v>104</v>
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t xml:space="preserve">311651315</t>
+          <t xml:space="preserve">311674697</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
@@ -17624,7 +17624,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-22</t>
+          <t xml:space="preserve">2033-04-19</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -17666,7 +17666,7 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oktobervej 95</t>
+          <t xml:space="preserve">Rådhus Alle 5</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
@@ -17676,30 +17676,30 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t xml:space="preserve">711965, 2099405</t>
+          <t xml:space="preserve">7003397</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J236">
-        <v>104</v>
+        <v>6392</v>
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674697</t>
+          <t xml:space="preserve">311688172</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Domutech A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-19</t>
+          <t xml:space="preserve">2033-06-15</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17741,40 +17741,40 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhus Alle 5</t>
+          <t xml:space="preserve">Nybrovej 356</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t xml:space="preserve">7003397</t>
+          <t xml:space="preserve">2087313</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J237">
-        <v>6392</v>
+        <v>517</v>
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t xml:space="preserve">311688172</t>
+          <t xml:space="preserve">311700222</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-15</t>
+          <t xml:space="preserve">2033-08-15</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17816,40 +17816,40 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nybrovej 356</t>
+          <t xml:space="preserve">Dynamovej 5</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t xml:space="preserve">2087313</t>
+          <t xml:space="preserve">711912, 2099459</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J238">
-        <v>517</v>
+        <v>1377</v>
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t xml:space="preserve">311700222</t>
+          <t xml:space="preserve">311710115</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Norca ApS</t>
         </is>
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-15</t>
+          <t xml:space="preserve">2033-09-25</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17906,15 +17906,15 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J239">
-        <v>1377</v>
+        <v>711</v>
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710115</t>
+          <t xml:space="preserve">311710118</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
@@ -17966,7 +17966,7 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dynamovej 5</t>
+          <t xml:space="preserve">Kildebakkegårds Alle 125</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
@@ -17976,30 +17976,30 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t xml:space="preserve">711912, 2099459</t>
+          <t xml:space="preserve">8528063</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J240">
-        <v>711</v>
+        <v>65</v>
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710118</t>
+          <t xml:space="preserve">311718752</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norca ApS</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-25</t>
+          <t xml:space="preserve">2033-10-31</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -18056,11 +18056,11 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J241">
-        <v>65</v>
+        <v>427</v>
       </c>
       <c r="K241" t="inlineStr">
         <is>
@@ -18116,7 +18116,7 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildebakkegårds Alle 125</t>
+          <t xml:space="preserve">Klausdalsbrovej 271</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
@@ -18126,20 +18126,20 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t xml:space="preserve">8528063</t>
+          <t xml:space="preserve">9522598</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J242">
-        <v>427</v>
+        <v>1385</v>
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t xml:space="preserve">311718752</t>
+          <t xml:space="preserve">311718754</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
@@ -18191,7 +18191,7 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klausdalsbrovej 271</t>
+          <t xml:space="preserve">Frødings Alle 8</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
@@ -18201,7 +18201,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t xml:space="preserve">9522598</t>
+          <t xml:space="preserve">2009885</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -18210,11 +18210,11 @@
         </is>
       </c>
       <c r="J243">
-        <v>1385</v>
+        <v>276</v>
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t xml:space="preserve">311718754</t>
+          <t xml:space="preserve">311720106</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
@@ -18224,7 +18224,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-31</t>
+          <t xml:space="preserve">2033-11-06</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -18266,7 +18266,7 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frødings Alle 8</t>
+          <t xml:space="preserve">Selma Lagerløfs Alle 14</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
@@ -18276,7 +18276,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t xml:space="preserve">2009885</t>
+          <t xml:space="preserve">2009605</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -18285,11 +18285,11 @@
         </is>
       </c>
       <c r="J244">
-        <v>276</v>
+        <v>108</v>
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t xml:space="preserve">311720106</t>
+          <t xml:space="preserve">311720234</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
@@ -18341,7 +18341,7 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selma Lagerløfs Alle 14</t>
+          <t xml:space="preserve">Signalvej 2</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
@@ -18351,7 +18351,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t xml:space="preserve">2009605</t>
+          <t xml:space="preserve">9883415</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -18360,11 +18360,11 @@
         </is>
       </c>
       <c r="J245">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t xml:space="preserve">311720234</t>
+          <t xml:space="preserve">311720237</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
@@ -18416,7 +18416,7 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Signalvej 2</t>
+          <t xml:space="preserve">Signalvej 4</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
@@ -18426,7 +18426,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t xml:space="preserve">9883415</t>
+          <t xml:space="preserve">9883416</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -18435,11 +18435,11 @@
         </is>
       </c>
       <c r="J246">
-        <v>98</v>
+        <v>144</v>
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t xml:space="preserve">311720237</t>
+          <t xml:space="preserve">311720239</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
@@ -18491,7 +18491,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Signalvej 4</t>
+          <t xml:space="preserve">Kildebakkegårds Alle 125</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
@@ -18501,7 +18501,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t xml:space="preserve">9883416</t>
+          <t xml:space="preserve">8528063</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -18510,11 +18510,11 @@
         </is>
       </c>
       <c r="J247">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t xml:space="preserve">311720239</t>
+          <t xml:space="preserve">311723524</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
@@ -18524,7 +18524,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-06</t>
+          <t xml:space="preserve">2033-11-20</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -18566,7 +18566,7 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildebakkegårds Alle 125</t>
+          <t xml:space="preserve">Kildebakken 20</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
@@ -18576,20 +18576,20 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t xml:space="preserve">8528063</t>
+          <t xml:space="preserve">7003397</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J248">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t xml:space="preserve">311723524</t>
+          <t xml:space="preserve">311724959</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
@@ -18599,7 +18599,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-20</t>
+          <t xml:space="preserve">2033-11-27</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -18641,7 +18641,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildebakken 20</t>
+          <t xml:space="preserve">Kildebakken 22</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
@@ -18656,15 +18656,15 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J249">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t xml:space="preserve">311724959</t>
+          <t xml:space="preserve">311724974</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
@@ -18716,7 +18716,7 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildebakken 22</t>
+          <t xml:space="preserve">Buddinge Hovedgade 133</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
@@ -18726,20 +18726,20 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t xml:space="preserve">7003397</t>
+          <t xml:space="preserve">2016445</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J250">
-        <v>126</v>
+        <v>196</v>
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t xml:space="preserve">311724974</t>
+          <t xml:space="preserve">311725195</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
@@ -18749,7 +18749,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-27</t>
+          <t xml:space="preserve">2033-11-28</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18791,7 +18791,7 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buddinge Hovedgade 133</t>
+          <t xml:space="preserve">Kellersvej 1</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
@@ -18801,20 +18801,20 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t xml:space="preserve">2016445</t>
+          <t xml:space="preserve">8777413</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J251">
-        <v>196</v>
+        <v>387</v>
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725195</t>
+          <t xml:space="preserve">311726616</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
@@ -18824,7 +18824,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-28</t>
+          <t xml:space="preserve">2033-12-04</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18866,7 +18866,7 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kellersvej 1</t>
+          <t xml:space="preserve">Kellersvej 6A</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
@@ -18881,15 +18881,15 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="J252">
-        <v>387</v>
+        <v>2082</v>
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t xml:space="preserve">311726616</t>
+          <t xml:space="preserve">311726596</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
@@ -18941,7 +18941,7 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kellersvej 6A</t>
+          <t xml:space="preserve">Kiplings Alle 6</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
@@ -18951,20 +18951,20 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777413</t>
+          <t xml:space="preserve">2013761</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J253">
-        <v>2082</v>
+        <v>236</v>
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t xml:space="preserve">311726596</t>
+          <t xml:space="preserve">311726600</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
@@ -19016,7 +19016,7 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kiplings Alle 6</t>
+          <t xml:space="preserve">Kong Hans Alle 45</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
@@ -19026,7 +19026,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t xml:space="preserve">2013761</t>
+          <t xml:space="preserve">2012391</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -19035,11 +19035,11 @@
         </is>
       </c>
       <c r="J254">
-        <v>236</v>
+        <v>625</v>
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t xml:space="preserve">311726600</t>
+          <t xml:space="preserve">311726743</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
@@ -19091,7 +19091,7 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kong Hans Alle 45</t>
+          <t xml:space="preserve">Kong Hans Alle 47</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
@@ -19106,15 +19106,15 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J255">
-        <v>625</v>
+        <v>638</v>
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t xml:space="preserve">311726743</t>
+          <t xml:space="preserve">311726742</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
@@ -19166,7 +19166,7 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kong Hans Alle 47</t>
+          <t xml:space="preserve">Lykkesborg Alle 9</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
@@ -19176,20 +19176,20 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t xml:space="preserve">2012391</t>
+          <t xml:space="preserve">2009675</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J256">
-        <v>638</v>
+        <v>242</v>
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t xml:space="preserve">311726742</t>
+          <t xml:space="preserve">311728248</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
@@ -19241,17 +19241,17 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lykkesborg Alle 9</t>
+          <t xml:space="preserve">Lupinmarken 11</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2880</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t xml:space="preserve">2009675</t>
+          <t xml:space="preserve">2018377</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -19260,11 +19260,11 @@
         </is>
       </c>
       <c r="J257">
-        <v>242</v>
+        <v>132</v>
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t xml:space="preserve">311728248</t>
+          <t xml:space="preserve">311726871</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
@@ -19274,7 +19274,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-04</t>
+          <t xml:space="preserve">2033-12-05</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -19316,30 +19316,30 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lupinmarken 11</t>
+          <t xml:space="preserve">Kellersvej 4</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t xml:space="preserve">2880</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t xml:space="preserve">2018377</t>
+          <t xml:space="preserve">8777413</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J258">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t xml:space="preserve">311726871</t>
+          <t xml:space="preserve">311727406</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
@@ -19349,7 +19349,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-05</t>
+          <t xml:space="preserve">2033-12-06</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -19391,7 +19391,7 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kellersvej 4</t>
+          <t xml:space="preserve">Kellersvej 8</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
@@ -19406,15 +19406,15 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="J259">
-        <v>128</v>
+        <v>176</v>
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t xml:space="preserve">311727406</t>
+          <t xml:space="preserve">311727397</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
@@ -19466,7 +19466,7 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kellersvej 8</t>
+          <t xml:space="preserve">Kildebakken 14</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
@@ -19476,20 +19476,20 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777413</t>
+          <t xml:space="preserve">7003397</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J260">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t xml:space="preserve">311727397</t>
+          <t xml:space="preserve">311727216</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
@@ -19541,7 +19541,7 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildebakken 14</t>
+          <t xml:space="preserve">Skolesvinget 10</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
@@ -19551,20 +19551,20 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t xml:space="preserve">7003397</t>
+          <t xml:space="preserve">8777389</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J261">
-        <v>160</v>
+        <v>1582</v>
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t xml:space="preserve">311727216</t>
+          <t xml:space="preserve">311727318</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
@@ -19616,7 +19616,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolesvinget 10</t>
+          <t xml:space="preserve">Høje Gladsaxe Torv 4</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
@@ -19631,15 +19631,15 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J262">
-        <v>1582</v>
+        <v>596</v>
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t xml:space="preserve">311727318</t>
+          <t xml:space="preserve">311728359</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
@@ -19649,7 +19649,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-06</t>
+          <t xml:space="preserve">2033-12-11</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -19706,15 +19706,15 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J263">
-        <v>596</v>
+        <v>9380</v>
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t xml:space="preserve">311728359</t>
+          <t xml:space="preserve">311728358</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
@@ -19766,30 +19766,30 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høje Gladsaxe Torv 4</t>
+          <t xml:space="preserve">Nybrovej 357</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777389</t>
+          <t xml:space="preserve">2089233</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J264">
-        <v>9380</v>
+        <v>112</v>
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t xml:space="preserve">311728358</t>
+          <t xml:space="preserve">311728271</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
@@ -19841,7 +19841,7 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nybrovej 357</t>
+          <t xml:space="preserve">Nybrovej 361</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
@@ -19856,15 +19856,15 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J265">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t xml:space="preserve">311728271</t>
+          <t xml:space="preserve">311728274</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
@@ -19916,30 +19916,30 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nybrovej 361</t>
+          <t xml:space="preserve">Pilegårdsvej 70</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t xml:space="preserve">2089233</t>
+          <t xml:space="preserve">2098080</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J266">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t xml:space="preserve">311728274</t>
+          <t xml:space="preserve">311728265</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
@@ -19991,7 +19991,7 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pilegårdsvej 70</t>
+          <t xml:space="preserve">Rådhus Alle 11</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
@@ -20001,20 +20001,20 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t xml:space="preserve">2098080</t>
+          <t xml:space="preserve">7003397</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J267">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t xml:space="preserve">311728265</t>
+          <t xml:space="preserve">311728264</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
@@ -20066,7 +20066,7 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhus Alle 11</t>
+          <t xml:space="preserve">Skolesvinget 15</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
@@ -20076,20 +20076,20 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t xml:space="preserve">7003397</t>
+          <t xml:space="preserve">100061953</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J268">
-        <v>132</v>
+        <v>1456</v>
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t xml:space="preserve">311728264</t>
+          <t xml:space="preserve">311728273</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
@@ -20141,7 +20141,7 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolesvinget 15</t>
+          <t xml:space="preserve">Skolesvinget 9</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
@@ -20151,20 +20151,20 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t xml:space="preserve">100061953</t>
+          <t xml:space="preserve">8777389</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J269">
-        <v>1456</v>
+        <v>830</v>
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t xml:space="preserve">311728273</t>
+          <t xml:space="preserve">311728269</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
@@ -20216,30 +20216,30 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolesvinget 9</t>
+          <t xml:space="preserve">Taxvej 23</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2880</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777389</t>
+          <t xml:space="preserve">2085253</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J270">
-        <v>830</v>
+        <v>180</v>
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t xml:space="preserve">311728269</t>
+          <t xml:space="preserve">311728291</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
@@ -20291,7 +20291,7 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taxvej 23</t>
+          <t xml:space="preserve">Til Jernbanen 20B</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
@@ -20301,20 +20301,20 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t xml:space="preserve">2085253</t>
+          <t xml:space="preserve">8777678</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J271">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t xml:space="preserve">311728291</t>
+          <t xml:space="preserve">311728270</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
@@ -20366,30 +20366,30 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t xml:space="preserve">Til Jernbanen 20B</t>
+          <t xml:space="preserve">Kellersvej 12</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t xml:space="preserve">2880</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777678</t>
+          <t xml:space="preserve">8777413</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c r="J272">
-        <v>90</v>
+        <v>356</v>
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t xml:space="preserve">311728270</t>
+          <t xml:space="preserve">311728443</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
@@ -20399,7 +20399,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-11</t>
+          <t xml:space="preserve">2033-12-12</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -20441,30 +20441,30 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kellersvej 12</t>
+          <t xml:space="preserve">Laurentsvej 9</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2880</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777413</t>
+          <t xml:space="preserve">1301832</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J273">
-        <v>356</v>
+        <v>180</v>
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t xml:space="preserve">311728443</t>
+          <t xml:space="preserve">311728529</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
@@ -20516,30 +20516,30 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laurentsvej 9</t>
+          <t xml:space="preserve">Søborg Hovedgade 190</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t xml:space="preserve">2880</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t xml:space="preserve">1301832</t>
+          <t xml:space="preserve">2013620</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J274">
-        <v>180</v>
+        <v>3508</v>
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t xml:space="preserve">311728529</t>
+          <t xml:space="preserve">311728546</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
@@ -20591,30 +20591,30 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søborg Hovedgade 190</t>
+          <t xml:space="preserve">Bagsværd Hovedgade 60F</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2880</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t xml:space="preserve">2013620</t>
+          <t xml:space="preserve">2087038</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J275">
-        <v>3508</v>
+        <v>1219</v>
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t xml:space="preserve">311728546</t>
+          <t xml:space="preserve">311728681</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
@@ -20624,7 +20624,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-12</t>
+          <t xml:space="preserve">2033-12-13</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -20666,30 +20666,30 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bagsværd Hovedgade 60F</t>
+          <t xml:space="preserve">Kellersvej 14</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t xml:space="preserve">2880</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t xml:space="preserve">2087038</t>
+          <t xml:space="preserve">8777413</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="J276">
-        <v>1219</v>
+        <v>894</v>
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t xml:space="preserve">311728681</t>
+          <t xml:space="preserve">311728910</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
@@ -20741,7 +20741,7 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kellersvej 14</t>
+          <t xml:space="preserve">Kellersvej 2</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
@@ -20756,15 +20756,15 @@
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J277">
-        <v>894</v>
+        <v>405</v>
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t xml:space="preserve">311728910</t>
+          <t xml:space="preserve">311728825</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
@@ -20816,7 +20816,7 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kellersvej 2</t>
+          <t xml:space="preserve">Kellersvej 20A</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
@@ -20831,15 +20831,15 @@
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J278">
-        <v>405</v>
+        <v>746</v>
       </c>
       <c r="K278" t="inlineStr">
         <is>
-          <t xml:space="preserve">311728825</t>
+          <t xml:space="preserve">311728826</t>
         </is>
       </c>
       <c r="L278" t="inlineStr">
@@ -20891,30 +20891,30 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kellersvej 20A</t>
+          <t xml:space="preserve">Nybrovej 315</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777413</t>
+          <t xml:space="preserve">2087317</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J279">
-        <v>746</v>
+        <v>160</v>
       </c>
       <c r="K279" t="inlineStr">
         <is>
-          <t xml:space="preserve">311728826</t>
+          <t xml:space="preserve">311728679</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
@@ -20966,7 +20966,7 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nybrovej 315</t>
+          <t xml:space="preserve">Nybrovej 384</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
@@ -20976,20 +20976,20 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t xml:space="preserve">2087317</t>
+          <t xml:space="preserve">711991, 7427504</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J280">
-        <v>160</v>
+        <v>548</v>
       </c>
       <c r="K280" t="inlineStr">
         <is>
-          <t xml:space="preserve">311728679</t>
+          <t xml:space="preserve">311728678</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
@@ -21041,30 +21041,30 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nybrovej 384</t>
+          <t xml:space="preserve">Gladsaxe Møllevej 127</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t xml:space="preserve">711991, 7427504</t>
+          <t xml:space="preserve">2016096</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J281">
-        <v>548</v>
+        <v>1032</v>
       </c>
       <c r="K281" t="inlineStr">
         <is>
-          <t xml:space="preserve">311728678</t>
+          <t xml:space="preserve">311729104</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
@@ -21074,7 +21074,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-13</t>
+          <t xml:space="preserve">2033-12-14</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -21116,7 +21116,7 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gladsaxe Møllevej 127</t>
+          <t xml:space="preserve">Kellersvej 10</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
@@ -21126,20 +21126,20 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t xml:space="preserve">2016096</t>
+          <t xml:space="preserve">8777413</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J282">
-        <v>1032</v>
+        <v>306</v>
       </c>
       <c r="K282" t="inlineStr">
         <is>
-          <t xml:space="preserve">311729104</t>
+          <t xml:space="preserve">311729024</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
@@ -21191,7 +21191,7 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kellersvej 10</t>
+          <t xml:space="preserve">Kellersvej 16</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
@@ -21206,15 +21206,15 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">29</t>
         </is>
       </c>
       <c r="J283">
-        <v>306</v>
+        <v>1077</v>
       </c>
       <c r="K283" t="inlineStr">
         <is>
-          <t xml:space="preserve">311729024</t>
+          <t xml:space="preserve">311729050</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
@@ -21266,7 +21266,7 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kellersvej 16</t>
+          <t xml:space="preserve">Kellersvej 18</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
@@ -21281,15 +21281,15 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t xml:space="preserve">29</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J284">
-        <v>1077</v>
+        <v>262</v>
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t xml:space="preserve">311729050</t>
+          <t xml:space="preserve">311728983</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
@@ -21341,7 +21341,7 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kellersvej 18</t>
+          <t xml:space="preserve">Kellersvej 22</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
@@ -21356,15 +21356,15 @@
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J285">
-        <v>262</v>
+        <v>208</v>
       </c>
       <c r="K285" t="inlineStr">
         <is>
-          <t xml:space="preserve">311728983</t>
+          <t xml:space="preserve">311728977</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
@@ -21416,30 +21416,30 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kellersvej 22</t>
+          <t xml:space="preserve">Kongshvilebakken 8</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777413</t>
+          <t xml:space="preserve">711944, 8777637</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J286">
-        <v>208</v>
+        <v>270</v>
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t xml:space="preserve">311728977</t>
+          <t xml:space="preserve">311729067</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
@@ -21491,7 +21491,7 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongshvilebakken 8</t>
+          <t xml:space="preserve">Bagsværd Møllevej 6</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
@@ -21501,20 +21501,20 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t xml:space="preserve">711944, 8777637</t>
+          <t xml:space="preserve">2087348</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="J287">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t xml:space="preserve">311729067</t>
+          <t xml:space="preserve">311729456</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
@@ -21524,7 +21524,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-14</t>
+          <t xml:space="preserve">2033-12-15</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -21566,35 +21566,35 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bagsværd Møllevej 6</t>
+          <t xml:space="preserve">Høje Gladsaxe 71</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t xml:space="preserve">2087348</t>
+          <t xml:space="preserve">7151445</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="J288">
-        <v>250</v>
+        <v>725</v>
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t xml:space="preserve">311729456</t>
+          <t xml:space="preserve">311729435</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Domutech A/S</t>
         </is>
       </c>
       <c r="M288" t="inlineStr">
@@ -21641,7 +21641,7 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høje Gladsaxe 71</t>
+          <t xml:space="preserve">Transformervej 1</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
@@ -21651,25 +21651,25 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t xml:space="preserve">7151445</t>
+          <t xml:space="preserve">8777493</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J289">
-        <v>725</v>
+        <v>393</v>
       </c>
       <c r="K289" t="inlineStr">
         <is>
-          <t xml:space="preserve">311729435</t>
+          <t xml:space="preserve">311729436</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t xml:space="preserve">Domutech A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M289" t="inlineStr">
@@ -21716,7 +21716,7 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transformervej 1</t>
+          <t xml:space="preserve">Transformervej 1B</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
@@ -21731,15 +21731,15 @@
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J290">
-        <v>393</v>
+        <v>872</v>
       </c>
       <c r="K290" t="inlineStr">
         <is>
-          <t xml:space="preserve">311729436</t>
+          <t xml:space="preserve">311729438</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
@@ -21791,17 +21791,17 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transformervej 1B</t>
+          <t xml:space="preserve">Bagsværdvej 144B</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777493</t>
+          <t xml:space="preserve">8777610</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -21810,11 +21810,11 @@
         </is>
       </c>
       <c r="J291">
-        <v>872</v>
+        <v>252</v>
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t xml:space="preserve">311729438</t>
+          <t xml:space="preserve">311730072</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
@@ -21824,7 +21824,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-15</t>
+          <t xml:space="preserve">2033-12-19</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -21866,30 +21866,30 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bagsværdvej 144B</t>
+          <t xml:space="preserve">Skolesvinget 8</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777610</t>
+          <t xml:space="preserve">8777389</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J292">
-        <v>252</v>
+        <v>3651</v>
       </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t xml:space="preserve">311730072</t>
+          <t xml:space="preserve">311730037</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
@@ -21941,7 +21941,7 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolesvinget 8</t>
+          <t xml:space="preserve">Isbanevej 8</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
@@ -21951,30 +21951,30 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777389</t>
+          <t xml:space="preserve">9123179</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J293">
-        <v>3651</v>
+        <v>5525</v>
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t xml:space="preserve">311730037</t>
+          <t xml:space="preserve">311730993</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Trykprøvning &amp; Energimærkning Danmark ApS</t>
         </is>
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-19</t>
+          <t xml:space="preserve">2033-12-22</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
@@ -22016,7 +22016,7 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isbanevej 8</t>
+          <t xml:space="preserve">Oktobervej 129</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
@@ -22026,30 +22026,30 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t xml:space="preserve">9123179</t>
+          <t xml:space="preserve">711973, 2099388</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J294">
-        <v>5525</v>
+        <v>103</v>
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t xml:space="preserve">311730993</t>
+          <t xml:space="preserve">311760991</t>
         </is>
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trykprøvning &amp; Energimærkning Danmark ApS</t>
+          <t xml:space="preserve">Domutech A/S</t>
         </is>
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-22</t>
+          <t xml:space="preserve">2034-05-22</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -22091,7 +22091,7 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oktobervej 129</t>
+          <t xml:space="preserve">Vandtårnsvej 55B</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
@@ -22101,30 +22101,30 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t xml:space="preserve">711973, 2099388</t>
+          <t xml:space="preserve">9123186</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="J295">
-        <v>103</v>
+        <v>1413</v>
       </c>
       <c r="K295" t="inlineStr">
         <is>
-          <t xml:space="preserve">311760991</t>
+          <t xml:space="preserve">311784035</t>
         </is>
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t xml:space="preserve">Domutech A/S</t>
+          <t xml:space="preserve">B.F. Byggeservice ApS</t>
         </is>
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-05-22</t>
+          <t xml:space="preserve">2034-09-11</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -22166,40 +22166,40 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vandtårnsvej 55B</t>
+          <t xml:space="preserve">Abelsvej 28</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2880</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t xml:space="preserve">9123186</t>
+          <t xml:space="preserve">2017381</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J296">
-        <v>1413</v>
+        <v>200</v>
       </c>
       <c r="K296" t="inlineStr">
         <is>
-          <t xml:space="preserve">311784035</t>
+          <t xml:space="preserve">311790382</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t xml:space="preserve">B.F. Byggeservice ApS</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-09-11</t>
+          <t xml:space="preserve">2034-10-09</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -22241,17 +22241,17 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t xml:space="preserve">Abelsvej 28</t>
+          <t xml:space="preserve">Runebergs Alle 22</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t xml:space="preserve">2880</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t xml:space="preserve">2017381</t>
+          <t xml:space="preserve">2009878</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -22260,11 +22260,11 @@
         </is>
       </c>
       <c r="J297">
-        <v>200</v>
+        <v>244</v>
       </c>
       <c r="K297" t="inlineStr">
         <is>
-          <t xml:space="preserve">311790382</t>
+          <t xml:space="preserve">311791318</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
@@ -22274,7 +22274,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-10-09</t>
+          <t xml:space="preserve">2034-10-14</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -22316,7 +22316,7 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t xml:space="preserve">Runebergs Alle 22</t>
+          <t xml:space="preserve">Kildebakkegårds Alle 155</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
@@ -22326,7 +22326,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t xml:space="preserve">2009878</t>
+          <t xml:space="preserve">2013423</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -22335,11 +22335,11 @@
         </is>
       </c>
       <c r="J298">
-        <v>244</v>
+        <v>10737</v>
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t xml:space="preserve">311791318</t>
+          <t xml:space="preserve">311791476</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
@@ -22349,7 +22349,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-10-14</t>
+          <t xml:space="preserve">2034-10-15</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -22406,15 +22406,15 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J299">
-        <v>10737</v>
+        <v>1176</v>
       </c>
       <c r="K299" t="inlineStr">
         <is>
-          <t xml:space="preserve">311791476</t>
+          <t xml:space="preserve">311791501</t>
         </is>
       </c>
       <c r="L299" t="inlineStr">
@@ -22466,7 +22466,7 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildebakkegårds Alle 155</t>
+          <t xml:space="preserve">Rådhus Alle 7</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
@@ -22476,20 +22476,20 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t xml:space="preserve">2013423</t>
+          <t xml:space="preserve">7003397</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J300">
-        <v>1176</v>
+        <v>7066</v>
       </c>
       <c r="K300" t="inlineStr">
         <is>
-          <t xml:space="preserve">311791501</t>
+          <t xml:space="preserve">311793436</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
@@ -22499,7 +22499,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-10-15</t>
+          <t xml:space="preserve">2034-10-25</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
@@ -22541,7 +22541,7 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhus Alle 7</t>
+          <t xml:space="preserve">Rådhuspassagen 6</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
@@ -22556,15 +22556,15 @@
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J301">
-        <v>7066</v>
+        <v>9307</v>
       </c>
       <c r="K301" t="inlineStr">
         <is>
-          <t xml:space="preserve">311793436</t>
+          <t xml:space="preserve">311793432</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">
@@ -22616,7 +22616,7 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhuspassagen 6</t>
+          <t xml:space="preserve">Turbinevej 12</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
@@ -22626,30 +22626,30 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t xml:space="preserve">7003397</t>
+          <t xml:space="preserve">2099385</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J302">
-        <v>9307</v>
+        <v>1460</v>
       </c>
       <c r="K302" t="inlineStr">
         <is>
-          <t xml:space="preserve">311793432</t>
+          <t xml:space="preserve">311798580</t>
         </is>
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-10-25</t>
+          <t xml:space="preserve">2034-11-21</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -22706,7 +22706,7 @@
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J303">
@@ -22766,7 +22766,7 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t xml:space="preserve">Turbinevej 12</t>
+          <t xml:space="preserve">Gladsaxe Møllevej 127</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
@@ -22776,30 +22776,30 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t xml:space="preserve">2099385</t>
+          <t xml:space="preserve">2016096</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J304">
-        <v>1460</v>
+        <v>7561</v>
       </c>
       <c r="K304" t="inlineStr">
         <is>
-          <t xml:space="preserve">311798580</t>
+          <t xml:space="preserve">311800880</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-11-21</t>
+          <t xml:space="preserve">2034-12-04</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -22841,7 +22841,7 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gladsaxe Møllevej 127</t>
+          <t xml:space="preserve">Kildebakkegårds Alle 165</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
@@ -22851,7 +22851,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t xml:space="preserve">2016096</t>
+          <t xml:space="preserve">2013620</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -22860,11 +22860,11 @@
         </is>
       </c>
       <c r="J305">
-        <v>7561</v>
+        <v>4085</v>
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t xml:space="preserve">311800880</t>
+          <t xml:space="preserve">311800877</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
@@ -22931,15 +22931,15 @@
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J306">
-        <v>4085</v>
+        <v>2565</v>
       </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t xml:space="preserve">311800877</t>
+          <t xml:space="preserve">311800876</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
@@ -22991,7 +22991,7 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildebakkegårds Alle 165</t>
+          <t xml:space="preserve">Klausdalsbrovej 213</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
@@ -23001,20 +23001,20 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t xml:space="preserve">2013620</t>
+          <t xml:space="preserve">8777475</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J307">
-        <v>2565</v>
+        <v>2718</v>
       </c>
       <c r="K307" t="inlineStr">
         <is>
-          <t xml:space="preserve">311800876</t>
+          <t xml:space="preserve">311800882</t>
         </is>
       </c>
       <c r="L307" t="inlineStr">
@@ -23081,11 +23081,11 @@
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J308">
-        <v>2718</v>
+        <v>3350</v>
       </c>
       <c r="K308" t="inlineStr">
         <is>
@@ -23156,15 +23156,15 @@
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J309">
-        <v>3350</v>
+        <v>361</v>
       </c>
       <c r="K309" t="inlineStr">
         <is>
-          <t xml:space="preserve">311800882</t>
+          <t xml:space="preserve">311800884</t>
         </is>
       </c>
       <c r="L309" t="inlineStr">
@@ -23216,7 +23216,7 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klausdalsbrovej 213</t>
+          <t xml:space="preserve">Kong Hans Alle 32</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
@@ -23226,20 +23226,20 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777475</t>
+          <t xml:space="preserve">1300233</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J310">
-        <v>361</v>
+        <v>4993</v>
       </c>
       <c r="K310" t="inlineStr">
         <is>
-          <t xml:space="preserve">311800884</t>
+          <t xml:space="preserve">311800878</t>
         </is>
       </c>
       <c r="L310" t="inlineStr">
@@ -23306,11 +23306,11 @@
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J311">
-        <v>4993</v>
+        <v>671</v>
       </c>
       <c r="K311" t="inlineStr">
         <is>
@@ -23381,11 +23381,11 @@
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J312">
-        <v>671</v>
+        <v>1431</v>
       </c>
       <c r="K312" t="inlineStr">
         <is>
@@ -23456,11 +23456,11 @@
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J313">
-        <v>1431</v>
+        <v>99</v>
       </c>
       <c r="K313" t="inlineStr">
         <is>
@@ -23516,7 +23516,7 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kong Hans Alle 32</t>
+          <t xml:space="preserve">Rådhus Alle 3</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
@@ -23526,20 +23526,20 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t xml:space="preserve">1300233</t>
+          <t xml:space="preserve">7003397</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J314">
-        <v>99</v>
+        <v>1062</v>
       </c>
       <c r="K314" t="inlineStr">
         <is>
-          <t xml:space="preserve">311800878</t>
+          <t xml:space="preserve">311800875</t>
         </is>
       </c>
       <c r="L314" t="inlineStr">
@@ -23591,30 +23591,30 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhus Alle 3</t>
+          <t xml:space="preserve">Slotsparken 32A</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2880</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t xml:space="preserve">7003397</t>
+          <t xml:space="preserve">8777643</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J315">
-        <v>1062</v>
+        <v>115</v>
       </c>
       <c r="K315" t="inlineStr">
         <is>
-          <t xml:space="preserve">311800875</t>
+          <t xml:space="preserve">311800965</t>
         </is>
       </c>
       <c r="L315" t="inlineStr">
@@ -23681,11 +23681,11 @@
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J316">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="K316" t="inlineStr">
         <is>
@@ -23741,22 +23741,22 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slotsparken 32A</t>
+          <t xml:space="preserve">Oktobervej 69</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t xml:space="preserve">2880</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777643</t>
+          <t xml:space="preserve">711961, 2099418</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J317">
@@ -23764,17 +23764,17 @@
       </c>
       <c r="K317" t="inlineStr">
         <is>
-          <t xml:space="preserve">311800965</t>
+          <t xml:space="preserve">311809629</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
         </is>
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-12-04</t>
+          <t xml:space="preserve">2035-02-04</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -23816,17 +23816,17 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oktobervej 69</t>
+          <t xml:space="preserve">Bagsværd Hovedgade 60</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2880</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t xml:space="preserve">711961, 2099418</t>
+          <t xml:space="preserve">2087038</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -23835,21 +23835,21 @@
         </is>
       </c>
       <c r="J318">
-        <v>103</v>
+        <v>11186</v>
       </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809629</t>
+          <t xml:space="preserve">311823120</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+          <t xml:space="preserve">OBH</t>
         </is>
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-02-04</t>
+          <t xml:space="preserve">2035-04-07</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -23891,7 +23891,7 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bagsværd Hovedgade 60</t>
+          <t xml:space="preserve">Taxvej 18</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
@@ -23901,30 +23901,30 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t xml:space="preserve">2087038</t>
+          <t xml:space="preserve">214564</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J319">
-        <v>11186</v>
+        <v>1369</v>
       </c>
       <c r="K319" t="inlineStr">
         <is>
-          <t xml:space="preserve">311823120</t>
+          <t xml:space="preserve">311823507</t>
         </is>
       </c>
       <c r="L319" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-07</t>
+          <t xml:space="preserve">2035-04-08</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -23966,7 +23966,7 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taxvej 18</t>
+          <t xml:space="preserve">Taxvej 20</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
@@ -23976,25 +23976,25 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t xml:space="preserve">214564</t>
+          <t xml:space="preserve">214566</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J320">
-        <v>1369</v>
+        <v>2076</v>
       </c>
       <c r="K320" t="inlineStr">
         <is>
-          <t xml:space="preserve">311823507</t>
+          <t xml:space="preserve">311823503</t>
         </is>
       </c>
       <c r="L320" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH</t>
         </is>
       </c>
       <c r="M320" t="inlineStr">
@@ -24041,30 +24041,30 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taxvej 20</t>
+          <t xml:space="preserve">Vadbro 37</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t xml:space="preserve">2880</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t xml:space="preserve">214566</t>
+          <t xml:space="preserve">8777417</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J321">
-        <v>2076</v>
+        <v>459</v>
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t xml:space="preserve">311823503</t>
+          <t xml:space="preserve">311823544</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
@@ -24116,40 +24116,40 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vadbro 37</t>
+          <t xml:space="preserve">Taxvej 18</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2880</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777417</t>
+          <t xml:space="preserve">214564, 214565</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J322">
-        <v>459</v>
+        <v>5862</v>
       </c>
       <c r="K322" t="inlineStr">
         <is>
-          <t xml:space="preserve">311823544</t>
+          <t xml:space="preserve">311824053</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-08</t>
+          <t xml:space="preserve">2035-04-09</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -24191,40 +24191,40 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taxvej 18</t>
+          <t xml:space="preserve">Telefonvej 14</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t xml:space="preserve">2880</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t xml:space="preserve">214564, 214565</t>
+          <t xml:space="preserve">214588</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J323">
-        <v>5862</v>
+        <v>8344</v>
       </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t xml:space="preserve">311824053</t>
+          <t xml:space="preserve">311830603</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH</t>
         </is>
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-09</t>
+          <t xml:space="preserve">2035-05-09</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -24266,40 +24266,40 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telefonvej 14</t>
+          <t xml:space="preserve">Bagsværd Møllevej 11</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t xml:space="preserve">214588</t>
+          <t xml:space="preserve">2087348</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="J324">
-        <v>8344</v>
+        <v>1686</v>
       </c>
       <c r="K324" t="inlineStr">
         <is>
-          <t xml:space="preserve">311830603</t>
+          <t xml:space="preserve">311851190</t>
         </is>
       </c>
       <c r="L324" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-09</t>
+          <t xml:space="preserve">2035-08-25</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -24341,7 +24341,7 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bagsværd Møllevej 11</t>
+          <t xml:space="preserve">Bagsværd Møllevej 9</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
@@ -24356,15 +24356,15 @@
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="J325">
-        <v>1686</v>
+        <v>408</v>
       </c>
       <c r="K325" t="inlineStr">
         <is>
-          <t xml:space="preserve">311851190</t>
+          <t xml:space="preserve">311851193</t>
         </is>
       </c>
       <c r="L325" t="inlineStr">
@@ -24431,11 +24431,11 @@
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="J326">
-        <v>408</v>
+        <v>648</v>
       </c>
       <c r="K326" t="inlineStr">
         <is>
@@ -24506,11 +24506,11 @@
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="J327">
-        <v>648</v>
+        <v>568</v>
       </c>
       <c r="K327" t="inlineStr">
         <is>
@@ -24581,15 +24581,15 @@
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="J328">
-        <v>568</v>
+        <v>248</v>
       </c>
       <c r="K328" t="inlineStr">
         <is>
-          <t xml:space="preserve">311851193</t>
+          <t xml:space="preserve">311851197</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
@@ -24656,11 +24656,11 @@
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="J329">
-        <v>248</v>
+        <v>728</v>
       </c>
       <c r="K329" t="inlineStr">
         <is>
@@ -24731,11 +24731,11 @@
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="J330">
-        <v>728</v>
+        <v>648</v>
       </c>
       <c r="K330" t="inlineStr">
         <is>
@@ -24806,11 +24806,11 @@
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="J331">
-        <v>648</v>
+        <v>488</v>
       </c>
       <c r="K331" t="inlineStr">
         <is>
@@ -24881,11 +24881,11 @@
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="J332">
-        <v>488</v>
+        <v>328</v>
       </c>
       <c r="K332" t="inlineStr">
         <is>
@@ -24956,15 +24956,15 @@
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="J333">
-        <v>328</v>
+        <v>2834</v>
       </c>
       <c r="K333" t="inlineStr">
         <is>
-          <t xml:space="preserve">311851197</t>
+          <t xml:space="preserve">311851188</t>
         </is>
       </c>
       <c r="L333" t="inlineStr">
@@ -25031,15 +25031,15 @@
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="J334">
-        <v>2834</v>
+        <v>60</v>
       </c>
       <c r="K334" t="inlineStr">
         <is>
-          <t xml:space="preserve">311851188</t>
+          <t xml:space="preserve">311851190</t>
         </is>
       </c>
       <c r="L334" t="inlineStr">
@@ -25091,30 +25091,30 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bagsværd Møllevej 9</t>
+          <t xml:space="preserve">Mørkhøjvej 332A</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t xml:space="preserve">2087348</t>
+          <t xml:space="preserve">2098044</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J335">
-        <v>60</v>
+        <v>1944</v>
       </c>
       <c r="K335" t="inlineStr">
         <is>
-          <t xml:space="preserve">311851190</t>
+          <t xml:space="preserve">311851178</t>
         </is>
       </c>
       <c r="L335" t="inlineStr">
@@ -25166,7 +25166,7 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mørkhøjvej 332A</t>
+          <t xml:space="preserve">Mørkhøjvej 336</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
@@ -25181,15 +25181,15 @@
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J336">
-        <v>1944</v>
+        <v>2374</v>
       </c>
       <c r="K336" t="inlineStr">
         <is>
-          <t xml:space="preserve">311851178</t>
+          <t xml:space="preserve">311851179</t>
         </is>
       </c>
       <c r="L336" t="inlineStr">
@@ -25256,15 +25256,15 @@
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J337">
-        <v>2374</v>
+        <v>3478</v>
       </c>
       <c r="K337" t="inlineStr">
         <is>
-          <t xml:space="preserve">311851179</t>
+          <t xml:space="preserve">311851180</t>
         </is>
       </c>
       <c r="L337" t="inlineStr">
@@ -25331,15 +25331,15 @@
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J338">
-        <v>3478</v>
+        <v>4327</v>
       </c>
       <c r="K338" t="inlineStr">
         <is>
-          <t xml:space="preserve">311851180</t>
+          <t xml:space="preserve">311851182</t>
         </is>
       </c>
       <c r="L338" t="inlineStr">
@@ -25391,7 +25391,7 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mørkhøjvej 336</t>
+          <t xml:space="preserve">Mørkhøjvej 336T</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
@@ -25406,15 +25406,15 @@
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J339">
-        <v>4327</v>
+        <v>750</v>
       </c>
       <c r="K339" t="inlineStr">
         <is>
-          <t xml:space="preserve">311851182</t>
+          <t xml:space="preserve">311851184</t>
         </is>
       </c>
       <c r="L339" t="inlineStr">
@@ -25466,7 +25466,7 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mørkhøjvej 336T</t>
+          <t xml:space="preserve">Turbinevej 12</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
@@ -25476,20 +25476,20 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t xml:space="preserve">2098044</t>
+          <t xml:space="preserve">2099385</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J340">
-        <v>750</v>
+        <v>430</v>
       </c>
       <c r="K340" t="inlineStr">
         <is>
-          <t xml:space="preserve">311851184</t>
+          <t xml:space="preserve">311852991</t>
         </is>
       </c>
       <c r="L340" t="inlineStr">
@@ -25499,7 +25499,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-25</t>
+          <t xml:space="preserve">2035-09-02</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -25541,7 +25541,7 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t xml:space="preserve">Turbinevej 12</t>
+          <t xml:space="preserve">Oktobervej 33</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
@@ -25551,30 +25551,30 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t xml:space="preserve">2099385</t>
+          <t xml:space="preserve">711950, 2099436</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J341">
-        <v>430</v>
+        <v>104</v>
       </c>
       <c r="K341" t="inlineStr">
         <is>
-          <t xml:space="preserve">311852991</t>
+          <t xml:space="preserve">311905187</t>
         </is>
       </c>
       <c r="L341" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
         </is>
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-09-02</t>
+          <t xml:space="preserve">2036-06-01</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -25616,7 +25616,7 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oktobervej 33</t>
+          <t xml:space="preserve">Mørkhøjvej 149</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
@@ -25626,7 +25626,7 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t xml:space="preserve">711950, 2099436</t>
+          <t xml:space="preserve">2098143</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -25635,21 +25635,21 @@
         </is>
       </c>
       <c r="J342">
-        <v>104</v>
+        <v>1146</v>
       </c>
       <c r="K342" t="inlineStr">
         <is>
-          <t xml:space="preserve">311905187</t>
+          <t xml:space="preserve">311909814</t>
         </is>
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+          <t xml:space="preserve">Norconsult Danmark A/S</t>
         </is>
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-01</t>
+          <t xml:space="preserve">2036-06-22</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -25691,17 +25691,17 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mørkhøjvej 149</t>
+          <t xml:space="preserve">Rylevænget 7B</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2880</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t xml:space="preserve">2098143</t>
+          <t xml:space="preserve">711974, 1300454</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -25710,21 +25710,21 @@
         </is>
       </c>
       <c r="J343">
-        <v>1146</v>
+        <v>113</v>
       </c>
       <c r="K343" t="inlineStr">
         <is>
-          <t xml:space="preserve">311909814</t>
+          <t xml:space="preserve">311928482</t>
         </is>
       </c>
       <c r="L343" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norconsult Danmark A/S</t>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
         </is>
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-22</t>
+          <t xml:space="preserve">2036-09-28</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
